--- a/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket_destination.xlsx
+++ b/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket_destination.xlsx
@@ -536,14 +536,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Batuque Town Villa 2</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>218182</v>
+        <v>182484</v>
       </c>
       <c r="E2" t="n">
-        <v>218182</v>
+        <v>182484</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>114000</v>
       </c>
       <c r="L2" t="n">
-        <v>6.34</v>
+        <v>6.49</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>14268</v>
+        <v>14593</v>
       </c>
       <c r="O2" t="n">
-        <v>450950</v>
+        <v>415577</v>
       </c>
       <c r="P2" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1549050</v>
+        <v>1084423</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -607,14 +607,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Kahan Homestay</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>219000</v>
+        <v>176740</v>
       </c>
       <c r="E3" t="n">
-        <v>219000</v>
+        <v>176740</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         <v>114000</v>
       </c>
       <c r="L3" t="n">
-        <v>6.74</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>15164</v>
+        <v>18864</v>
       </c>
       <c r="O3" t="n">
-        <v>452664</v>
+        <v>414104</v>
       </c>
       <c r="P3" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1547336</v>
+        <v>1085896</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -678,14 +678,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Family Homestay Arya</t>
+          <t>Super OYO 604 Cemara's Homestay</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>220925</v>
+        <v>182496</v>
       </c>
       <c r="E4" t="n">
-        <v>220925</v>
+        <v>182496</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>114000</v>
       </c>
       <c r="L4" t="n">
-        <v>8.27</v>
+        <v>8.65</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -718,16 +718,16 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>18599</v>
+        <v>19466</v>
       </c>
       <c r="O4" t="n">
-        <v>458024</v>
+        <v>420462</v>
       </c>
       <c r="P4" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1541976</v>
+        <v>1079538</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -749,14 +749,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rosetta Villa &amp; Homestay</t>
+          <t>RedDoorz Plus near Balai Kota Batu 2</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>215000</v>
+        <v>180000</v>
       </c>
       <c r="E5" t="n">
-        <v>215000</v>
+        <v>180000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>114000</v>
       </c>
       <c r="L5" t="n">
-        <v>11.54</v>
+        <v>11.02</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -789,16 +789,16 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>25961</v>
+        <v>24795</v>
       </c>
       <c r="O5" t="n">
-        <v>459461</v>
+        <v>423295</v>
       </c>
       <c r="P5" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1540539</v>
+        <v>1076705</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -820,14 +820,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rayana Resort</t>
+          <t>SR Guesthouse</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>220875</v>
+        <v>173966</v>
       </c>
       <c r="E6" t="n">
-        <v>220875</v>
+        <v>173966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>114000</v>
       </c>
       <c r="L6" t="n">
-        <v>16.08</v>
+        <v>11.03</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -860,16 +860,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>36177</v>
+        <v>24820</v>
       </c>
       <c r="O6" t="n">
-        <v>475552</v>
+        <v>417286</v>
       </c>
       <c r="P6" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q6" t="n">
-        <v>1524448</v>
+        <v>1082714</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -891,14 +891,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Kahan Homestay</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>219000</v>
+        <v>176740</v>
       </c>
       <c r="E7" t="n">
-        <v>219000</v>
+        <v>176740</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>114000</v>
       </c>
       <c r="L7" t="n">
-        <v>30.16</v>
+        <v>30.26</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>67854</v>
+        <v>68075</v>
       </c>
       <c r="O7" t="n">
-        <v>505354</v>
+        <v>463315</v>
       </c>
       <c r="P7" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q7" t="n">
-        <v>1494646</v>
+        <v>1036685</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -962,14 +962,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Family Homestay Arya</t>
+          <t>Super OYO 604 Cemara's Homestay</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>220925</v>
+        <v>182496</v>
       </c>
       <c r="E8" t="n">
-        <v>220925</v>
+        <v>182496</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>114000</v>
       </c>
       <c r="L8" t="n">
-        <v>30.34</v>
+        <v>30.28</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>68263</v>
+        <v>68130</v>
       </c>
       <c r="O8" t="n">
-        <v>507688</v>
+        <v>469126</v>
       </c>
       <c r="P8" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q8" t="n">
-        <v>1492312</v>
+        <v>1030874</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1033,14 +1033,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Batuque Town Villa 2</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>218182</v>
+        <v>182484</v>
       </c>
       <c r="E9" t="n">
-        <v>218182</v>
+        <v>182484</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>114000</v>
       </c>
       <c r="L9" t="n">
-        <v>31.32</v>
+        <v>32</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>70479</v>
+        <v>72006</v>
       </c>
       <c r="O9" t="n">
-        <v>507161</v>
+        <v>472990</v>
       </c>
       <c r="P9" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q9" t="n">
-        <v>1492839</v>
+        <v>1027010</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1104,14 +1104,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rosetta Villa &amp; Homestay</t>
+          <t>SR Guesthouse</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>215000</v>
+        <v>173966</v>
       </c>
       <c r="E10" t="n">
-        <v>215000</v>
+        <v>173966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>114000</v>
       </c>
       <c r="L10" t="n">
-        <v>36.21</v>
+        <v>34.86</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1144,16 +1144,16 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>81472</v>
+        <v>78443</v>
       </c>
       <c r="O10" t="n">
-        <v>514972</v>
+        <v>470909</v>
       </c>
       <c r="P10" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q10" t="n">
-        <v>1485028</v>
+        <v>1029091</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1175,14 +1175,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Batuque Town Villa 2</t>
+          <t>RedDoorz Plus near Balai Kota Batu 2</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>218182</v>
+        <v>180000</v>
       </c>
       <c r="E11" t="n">
-        <v>218182</v>
+        <v>180000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Warung Lalapan Mbak Denok</t>
+          <t>Depot 200</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1207,7 +1207,7 @@
         <v>114000</v>
       </c>
       <c r="L11" t="n">
-        <v>36.28</v>
+        <v>35.33</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1215,16 +1215,16 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>81627</v>
+        <v>79497</v>
       </c>
       <c r="O11" t="n">
-        <v>518309</v>
+        <v>477997</v>
       </c>
       <c r="P11" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q11" t="n">
-        <v>1481691</v>
+        <v>1022003</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1246,14 +1246,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rosetta Villa &amp; Homestay</t>
+          <t>RedDoorz Syariah @ Soekarno Hatta Indah 2</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>215000</v>
+        <v>180000</v>
       </c>
       <c r="E12" t="n">
-        <v>215000</v>
+        <v>180000</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Warung Lalapan Mbak Denok</t>
+          <t>Depot 200</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1278,7 +1278,7 @@
         <v>114000</v>
       </c>
       <c r="L12" t="n">
-        <v>36.4</v>
+        <v>35.83</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1286,16 +1286,16 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>81893</v>
+        <v>80608</v>
       </c>
       <c r="O12" t="n">
-        <v>515393</v>
+        <v>479108</v>
       </c>
       <c r="P12" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q12" t="n">
-        <v>1484607</v>
+        <v>1020892</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1317,14 +1317,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>RedDoorz Plus near Balai Kota Batu 2</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>219000</v>
+        <v>180000</v>
       </c>
       <c r="E13" t="n">
-        <v>219000</v>
+        <v>180000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>114000</v>
       </c>
       <c r="L13" t="n">
-        <v>37.3</v>
+        <v>36.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1357,16 +1357,16 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>83915</v>
+        <v>82566</v>
       </c>
       <c r="O13" t="n">
-        <v>521415</v>
+        <v>481066</v>
       </c>
       <c r="P13" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q13" t="n">
-        <v>1478585</v>
+        <v>1018934</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1388,14 +1388,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New Bandahara Exclusive</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>220000</v>
+        <v>182484</v>
       </c>
       <c r="E14" t="n">
-        <v>220000</v>
+        <v>182484</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Kedai Kopi Mbok gandul tujinem</t>
+          <t>Warung Lalapan Mbak Denok</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1420,7 +1420,7 @@
         <v>114000</v>
       </c>
       <c r="L14" t="n">
-        <v>37.62</v>
+        <v>37.12</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>84641</v>
+        <v>83515</v>
       </c>
       <c r="O14" t="n">
-        <v>523141</v>
+        <v>484499</v>
       </c>
       <c r="P14" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q14" t="n">
-        <v>1476859</v>
+        <v>1015501</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1459,14 +1459,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rayana Resort</t>
+          <t>SR Guesthouse</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>220875</v>
+        <v>173966</v>
       </c>
       <c r="E15" t="n">
-        <v>220875</v>
+        <v>173966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>114000</v>
       </c>
       <c r="L15" t="n">
-        <v>37.72</v>
+        <v>37.28</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1499,16 +1499,16 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>84880</v>
+        <v>83890</v>
       </c>
       <c r="O15" t="n">
-        <v>524255</v>
+        <v>476356</v>
       </c>
       <c r="P15" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q15" t="n">
-        <v>1475745</v>
+        <v>1023644</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1530,14 +1530,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ratu Boarding House &amp; Homestay</t>
+          <t>RedDoorz Syariah @ Soekarno Hatta Indah 2</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>220000</v>
+        <v>180000</v>
       </c>
       <c r="E16" t="n">
-        <v>220000</v>
+        <v>180000</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Depot 200</t>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1562,7 +1562,7 @@
         <v>114000</v>
       </c>
       <c r="L16" t="n">
-        <v>37.85</v>
+        <v>37.33</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1570,16 +1570,16 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>85154</v>
+        <v>84001</v>
       </c>
       <c r="O16" t="n">
-        <v>523654</v>
+        <v>482501</v>
       </c>
       <c r="P16" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q16" t="n">
-        <v>1476346</v>
+        <v>1017499</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1601,14 +1601,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kusuma Agrowisata Resort &amp; Convention Hotel</t>
+          <t>Urbanview Syariah Kanigara Guesthouse</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>657777</v>
+        <v>314618</v>
       </c>
       <c r="E17" t="n">
-        <v>657777</v>
+        <v>314618</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>215400</v>
       </c>
       <c r="L17" t="n">
-        <v>2.14</v>
+        <v>1.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4817</v>
+        <v>2711</v>
       </c>
       <c r="O17" t="n">
-        <v>982494</v>
+        <v>637229</v>
       </c>
       <c r="P17" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q17" t="n">
-        <v>1017506</v>
+        <v>862771</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1672,14 +1672,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oak Tree Glamping Resort</t>
+          <t>Urbanview Syariah Kanigara Guesthouse</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>710100</v>
+        <v>314618</v>
       </c>
       <c r="E18" t="n">
-        <v>710100</v>
+        <v>314618</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1694,17 +1694,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DEPOT MAMAKU AYAM GORENG DAN NASI TIMBEL</t>
+          <t>Ayam Goreng Pemuda</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>35900</v>
+        <v>33750</v>
       </c>
       <c r="K18" t="n">
-        <v>215400</v>
+        <v>202500</v>
       </c>
       <c r="L18" t="n">
-        <v>4.48</v>
+        <v>3.68</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>10086</v>
+        <v>8287</v>
       </c>
       <c r="O18" t="n">
-        <v>1040086</v>
+        <v>629905</v>
       </c>
       <c r="P18" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q18" t="n">
-        <v>959914</v>
+        <v>870095</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1743,14 +1743,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hanoman Kota Batu</t>
+          <t>Azana BeSt Hotel Batu</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>717973</v>
+        <v>318644</v>
       </c>
       <c r="E19" t="n">
-        <v>717973</v>
+        <v>318644</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>215400</v>
       </c>
       <c r="L19" t="n">
-        <v>5.8</v>
+        <v>10.28</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1783,16 +1783,16 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>13060</v>
+        <v>23140</v>
       </c>
       <c r="O19" t="n">
-        <v>1050933</v>
+        <v>661684</v>
       </c>
       <c r="P19" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q19" t="n">
-        <v>949067</v>
+        <v>838316</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -1814,14 +1814,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kintamani 360 Villa &amp; Guest House Syariah</t>
+          <t>Grand Pujon View Hotel and Resort</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>600000</v>
+        <v>314885</v>
       </c>
       <c r="E20" t="n">
-        <v>600000</v>
+        <v>314885</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>215400</v>
       </c>
       <c r="L20" t="n">
-        <v>6.82</v>
+        <v>10.64</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1854,16 +1854,16 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>15339</v>
+        <v>23939</v>
       </c>
       <c r="O20" t="n">
-        <v>935239</v>
+        <v>658724</v>
       </c>
       <c r="P20" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q20" t="n">
-        <v>1064761</v>
+        <v>841276</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -1885,14 +1885,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Maniva Particael Resort</t>
+          <t>Dedaunan Guest House</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>600000</v>
+        <v>309295</v>
       </c>
       <c r="E21" t="n">
-        <v>600000</v>
+        <v>309295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>215400</v>
       </c>
       <c r="L21" t="n">
-        <v>7.93</v>
+        <v>12.94</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1925,16 +1925,16 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>17833</v>
+        <v>29108</v>
       </c>
       <c r="O21" t="n">
-        <v>937733</v>
+        <v>658303</v>
       </c>
       <c r="P21" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q21" t="n">
-        <v>1062267</v>
+        <v>841697</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -1956,14 +1956,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Villa Puncak Pinus And Pool</t>
+          <t>Azana BeSt Hotel Batu</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>650000</v>
+        <v>318644</v>
       </c>
       <c r="E22" t="n">
-        <v>650000</v>
+        <v>318644</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1978,17 +1978,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DEPOT MAMAKU AYAM GORENG DAN NASI TIMBEL</t>
+          <t>Ayam Goreng Pemuda</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>35900</v>
+        <v>33750</v>
       </c>
       <c r="K22" t="n">
-        <v>215400</v>
+        <v>202500</v>
       </c>
       <c r="L22" t="n">
-        <v>8.49</v>
+        <v>11.26</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1996,16 +1996,16 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>19097</v>
+        <v>25324</v>
       </c>
       <c r="O22" t="n">
-        <v>988997</v>
+        <v>650968</v>
       </c>
       <c r="P22" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q22" t="n">
-        <v>1011003</v>
+        <v>849032</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2027,14 +2027,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oak Tree Glamping Resort</t>
+          <t>Grand Pujon View Hotel and Resort</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>710100</v>
+        <v>314885</v>
       </c>
       <c r="E23" t="n">
-        <v>710100</v>
+        <v>314885</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>202500</v>
       </c>
       <c r="L23" t="n">
-        <v>4.79</v>
+        <v>12.54</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2067,16 +2067,16 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>10770</v>
+        <v>28210</v>
       </c>
       <c r="O23" t="n">
-        <v>1027870</v>
+        <v>650095</v>
       </c>
       <c r="P23" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q23" t="n">
-        <v>972130</v>
+        <v>849905</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2098,14 +2098,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kusuma Agrowisata Resort &amp; Convention Hotel</t>
+          <t>Dedaunan Guest House</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>657777</v>
+        <v>309295</v>
       </c>
       <c r="E24" t="n">
-        <v>657777</v>
+        <v>309295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>202500</v>
       </c>
       <c r="L24" t="n">
-        <v>5.14</v>
+        <v>14.16</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2138,16 +2138,16 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>11572</v>
+        <v>31861</v>
       </c>
       <c r="O24" t="n">
-        <v>976349</v>
+        <v>648156</v>
       </c>
       <c r="P24" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q24" t="n">
-        <v>1023651</v>
+        <v>851844</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hanoman Kota Batu</t>
+          <t>Grand Pujon View Hotel and Resort</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>717973</v>
+        <v>314885</v>
       </c>
       <c r="E25" t="n">
-        <v>717973</v>
+        <v>314885</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2191,17 +2191,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Ayam Goreng Pemuda</t>
+          <t>Rumah Makan Weringin Asri</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>33750</v>
+        <v>34000</v>
       </c>
       <c r="K25" t="n">
-        <v>202500</v>
+        <v>204000</v>
       </c>
       <c r="L25" t="n">
-        <v>6.12</v>
+        <v>11.88</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2209,16 +2209,16 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>13772</v>
+        <v>26726</v>
       </c>
       <c r="O25" t="n">
-        <v>1038745</v>
+        <v>650111</v>
       </c>
       <c r="P25" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q25" t="n">
-        <v>961255</v>
+        <v>849889</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2240,14 +2240,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Purnama Hotel</t>
+          <t>Urbanview Syariah Kanigara Guesthouse</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>600000</v>
+        <v>314618</v>
       </c>
       <c r="E26" t="n">
-        <v>600000</v>
+        <v>314618</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2262,17 +2262,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>DEPOT MAMAKU AYAM GORENG DAN NASI TIMBEL</t>
+          <t>Rumah Makan Weringin Asri</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>35900</v>
+        <v>34000</v>
       </c>
       <c r="K26" t="n">
-        <v>215400</v>
+        <v>204000</v>
       </c>
       <c r="L26" t="n">
-        <v>11.46</v>
+        <v>11.95</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2280,16 +2280,16 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>25793</v>
+        <v>26883</v>
       </c>
       <c r="O26" t="n">
-        <v>945693</v>
+        <v>650001</v>
       </c>
       <c r="P26" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q26" t="n">
-        <v>1054307</v>
+        <v>849999</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2311,14 +2311,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kintamani 360 Villa &amp; Guest House Syariah</t>
+          <t>Urbanview Syariah Kanigara Guesthouse</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>600000</v>
+        <v>314618</v>
       </c>
       <c r="E27" t="n">
-        <v>600000</v>
+        <v>314618</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2333,17 +2333,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Ayam Goreng Pemuda</t>
+          <t>Warung Pring Pethuk</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>33750</v>
+        <v>34375</v>
       </c>
       <c r="K27" t="n">
-        <v>202500</v>
+        <v>206250</v>
       </c>
       <c r="L27" t="n">
-        <v>6.86</v>
+        <v>8.48</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2351,16 +2351,16 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>15424</v>
+        <v>19090</v>
       </c>
       <c r="O27" t="n">
-        <v>922424</v>
+        <v>644458</v>
       </c>
       <c r="P27" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q27" t="n">
-        <v>1077576</v>
+        <v>855542</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -2382,14 +2382,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Maniva Particael Resort</t>
+          <t>Grand Pujon View Hotel and Resort</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>600000</v>
+        <v>314885</v>
       </c>
       <c r="E28" t="n">
-        <v>600000</v>
+        <v>314885</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2404,17 +2404,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Ayam Goreng Pemuda</t>
+          <t>Warung Pring Pethuk</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>33750</v>
+        <v>34375</v>
       </c>
       <c r="K28" t="n">
-        <v>202500</v>
+        <v>206250</v>
       </c>
       <c r="L28" t="n">
-        <v>8.949999999999999</v>
+        <v>13.48</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2422,16 +2422,16 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>20146</v>
+        <v>30325</v>
       </c>
       <c r="O28" t="n">
-        <v>927146</v>
+        <v>655960</v>
       </c>
       <c r="P28" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q28" t="n">
-        <v>1072854</v>
+        <v>844040</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2453,14 +2453,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Villa Puncak Pinus And Pool</t>
+          <t>RedDoorz Plus near Brawijaya Museum</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>650000</v>
+        <v>313066</v>
       </c>
       <c r="E29" t="n">
-        <v>650000</v>
+        <v>313066</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2475,17 +2475,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Ayam Goreng Pemuda</t>
+          <t>Pondok Desa</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>33750</v>
+        <v>35000</v>
       </c>
       <c r="K29" t="n">
-        <v>202500</v>
+        <v>210000</v>
       </c>
       <c r="L29" t="n">
-        <v>10.95</v>
+        <v>41.33</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2493,16 +2493,16 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>24639</v>
+        <v>93002</v>
       </c>
       <c r="O29" t="n">
-        <v>981639</v>
+        <v>720568</v>
       </c>
       <c r="P29" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q29" t="n">
-        <v>1018361</v>
+        <v>779432</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2524,14 +2524,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Purnama Hotel</t>
+          <t>Semeru Hostel Malang</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>600000</v>
+        <v>307162</v>
       </c>
       <c r="E30" t="n">
-        <v>600000</v>
+        <v>307162</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2546,17 +2546,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Ayam Goreng Pemuda</t>
+          <t>Pondok Desa</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>33750</v>
+        <v>35000</v>
       </c>
       <c r="K30" t="n">
-        <v>202500</v>
+        <v>210000</v>
       </c>
       <c r="L30" t="n">
-        <v>11.86</v>
+        <v>41.56</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2564,16 +2564,16 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>26680</v>
+        <v>93499</v>
       </c>
       <c r="O30" t="n">
-        <v>933680</v>
+        <v>715161</v>
       </c>
       <c r="P30" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q30" t="n">
-        <v>1066320</v>
+        <v>784839</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2595,14 +2595,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kapal Garden Hotel</t>
+          <t>Dedaunan Guest House</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>581554</v>
+        <v>309295</v>
       </c>
       <c r="E31" t="n">
-        <v>581554</v>
+        <v>309295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2617,17 +2617,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DEPOT MAMAKU AYAM GORENG DAN NASI TIMBEL</t>
+          <t>Pondok Desa</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>35900</v>
+        <v>35000</v>
       </c>
       <c r="K31" t="n">
-        <v>215400</v>
+        <v>210000</v>
       </c>
       <c r="L31" t="n">
-        <v>22.3</v>
+        <v>41.57</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>50170</v>
+        <v>93540</v>
       </c>
       <c r="O31" t="n">
-        <v>951624</v>
+        <v>717335</v>
       </c>
       <c r="P31" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q31" t="n">
-        <v>1048376</v>
+        <v>782665</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kanana Retreat</t>
+          <t>Sea Villa Kota Batu</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1511714</v>
+        <v>1000000</v>
       </c>
       <c r="E32" t="n">
-        <v>1511714</v>
+        <v>1000000</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2688,17 +2688,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Kutaraja Boutique Restaurant</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>51182</v>
+        <v>53500</v>
       </c>
       <c r="K32" t="n">
-        <v>307092</v>
+        <v>321000</v>
       </c>
       <c r="L32" t="n">
-        <v>11.5</v>
+        <v>10.4</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2706,16 +2706,16 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>25865</v>
+        <v>23405</v>
       </c>
       <c r="O32" t="n">
-        <v>1949171</v>
+        <v>1448905</v>
       </c>
       <c r="P32" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q32" t="n">
-        <v>50829</v>
+        <v>51095</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -2737,14 +2737,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kanana Retreat</t>
+          <t>Sea Villa Kota Batu</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1511714</v>
+        <v>1000000</v>
       </c>
       <c r="E33" t="n">
-        <v>1511714</v>
+        <v>1000000</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2759,17 +2759,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Kutaraja Boutique Restaurant</t>
+          <t>De Bamboo Restaurant</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>53500</v>
+        <v>51182</v>
       </c>
       <c r="K33" t="n">
-        <v>321000</v>
+        <v>307092</v>
       </c>
       <c r="L33" t="n">
-        <v>20.01</v>
+        <v>11.58</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2777,16 +2777,16 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>45031</v>
+        <v>26066</v>
       </c>
       <c r="O33" t="n">
-        <v>1982245</v>
+        <v>1437658</v>
       </c>
       <c r="P33" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q33" t="n">
-        <v>17755</v>
+        <v>62342</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -2808,14 +2808,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Batu View Villa</t>
+          <t>Sea Villa Kota Batu</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="E34" t="n">
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2830,17 +2830,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot Widari</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>51182</v>
+        <v>50600</v>
       </c>
       <c r="K34" t="n">
-        <v>307092</v>
+        <v>303600</v>
       </c>
       <c r="L34" t="n">
-        <v>8.52</v>
+        <v>40.11</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>19162</v>
+        <v>90250</v>
       </c>
       <c r="O34" t="n">
-        <v>1930754</v>
+        <v>1498350</v>
       </c>
       <c r="P34" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q34" t="n">
-        <v>69246</v>
+        <v>1650</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -2879,14 +2879,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Batu View Villa</t>
+          <t>BeSS Resort and Waterpark</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1500000</v>
+        <v>932942</v>
       </c>
       <c r="E35" t="n">
-        <v>1500000</v>
+        <v>932942</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Kutaraja Boutique Restaurant</t>
+          <t>De Bamboo Restaurant</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>53500</v>
+        <v>51182</v>
       </c>
       <c r="K35" t="n">
-        <v>321000</v>
+        <v>307092</v>
       </c>
       <c r="L35" t="n">
-        <v>11.55</v>
+        <v>64.47</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2919,16 +2919,16 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>25986</v>
+        <v>145054</v>
       </c>
       <c r="O35" t="n">
-        <v>1951486</v>
+        <v>1489588</v>
       </c>
       <c r="P35" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q35" t="n">
-        <v>48514</v>
+        <v>10412</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -2950,14 +2950,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Farbel Homestay</t>
+          <t>Kos Griya Gangsar Kepanjen Malang</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1500000</v>
+        <v>900000</v>
       </c>
       <c r="E36" t="n">
-        <v>1500000</v>
+        <v>900000</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>321000</v>
       </c>
       <c r="L36" t="n">
-        <v>12.24</v>
+        <v>77.31</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>27533</v>
+        <v>173943</v>
       </c>
       <c r="O36" t="n">
-        <v>1953033</v>
+        <v>1499443</v>
       </c>
       <c r="P36" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q36" t="n">
-        <v>46967</v>
+        <v>557</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -3021,14 +3021,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Farbel Homestay</t>
+          <t>Kos Griya Gangsar Kepanjen Malang</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1500000</v>
+        <v>900000</v>
       </c>
       <c r="E37" t="n">
-        <v>1500000</v>
+        <v>900000</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>307092</v>
       </c>
       <c r="L37" t="n">
-        <v>14.64</v>
+        <v>79.27</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3061,16 +3061,16 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>32950</v>
+        <v>178349</v>
       </c>
       <c r="O37" t="n">
-        <v>1944542</v>
+        <v>1489941</v>
       </c>
       <c r="P37" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q37" t="n">
-        <v>55458</v>
+        <v>10059</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -3092,14 +3092,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Villa Melinda Home Stay</t>
+          <t>Kos Griya Gangsar Kepanjen Malang</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1500000</v>
+        <v>900000</v>
       </c>
       <c r="E38" t="n">
-        <v>1500000</v>
+        <v>900000</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3114,17 +3114,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot Widari</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>51182</v>
+        <v>50600</v>
       </c>
       <c r="K38" t="n">
-        <v>307092</v>
+        <v>303600</v>
       </c>
       <c r="L38" t="n">
-        <v>17.67</v>
+        <v>81.89</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3132,16 +3132,16 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>39758</v>
+        <v>184248</v>
       </c>
       <c r="O38" t="n">
-        <v>1951350</v>
+        <v>1492348</v>
       </c>
       <c r="P38" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q38" t="n">
-        <v>48650</v>
+        <v>7652</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3163,14 +3163,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Villa Melinda Home Stay</t>
+          <t>Bobocabin Coban Rondo, Malang</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1500000</v>
+        <v>813000</v>
       </c>
       <c r="E39" t="n">
-        <v>1500000</v>
+        <v>813000</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3185,17 +3185,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Kutaraja Boutique Restaurant</t>
+          <t>De Bamboo Restaurant</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>53500</v>
+        <v>51182</v>
       </c>
       <c r="K39" t="n">
-        <v>321000</v>
+        <v>307092</v>
       </c>
       <c r="L39" t="n">
-        <v>24.34</v>
+        <v>10.4</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3203,16 +3203,16 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>54775</v>
+        <v>23401</v>
       </c>
       <c r="O39" t="n">
-        <v>1980275</v>
+        <v>1247993</v>
       </c>
       <c r="P39" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q39" t="n">
-        <v>19725</v>
+        <v>252007</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -3234,14 +3234,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Farbel Homestay</t>
+          <t>Bobocabin Coban Rondo, Malang</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1500000</v>
+        <v>813000</v>
       </c>
       <c r="E40" t="n">
-        <v>1500000</v>
+        <v>813000</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3256,17 +3256,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Depot Widari</t>
+          <t>Sop Janda Suroboyo - BATU MALANG</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>50600</v>
+        <v>68500</v>
       </c>
       <c r="K40" t="n">
-        <v>303600</v>
+        <v>411000</v>
       </c>
       <c r="L40" t="n">
-        <v>40.16</v>
+        <v>12.33</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3274,16 +3274,16 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>90354</v>
+        <v>27739</v>
       </c>
       <c r="O40" t="n">
-        <v>1998454</v>
+        <v>1356239</v>
       </c>
       <c r="P40" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q40" t="n">
-        <v>1546</v>
+        <v>143761</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -3305,14 +3305,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>The Onsen Hot Spring Resort Songgoriti</t>
+          <t>Bobocabin Coban Rondo, Malang</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1446507</v>
+        <v>813000</v>
       </c>
       <c r="E41" t="n">
-        <v>1446507</v>
+        <v>813000</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3327,17 +3327,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Kutaraja Boutique Restaurant</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>51182</v>
+        <v>53500</v>
       </c>
       <c r="K41" t="n">
-        <v>307092</v>
+        <v>321000</v>
       </c>
       <c r="L41" t="n">
-        <v>7.22</v>
+        <v>19.32</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3345,16 +3345,16 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>16252</v>
+        <v>43465</v>
       </c>
       <c r="O41" t="n">
-        <v>1874351</v>
+        <v>1281965</v>
       </c>
       <c r="P41" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q41" t="n">
-        <v>125649</v>
+        <v>218035</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3376,14 +3376,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>The Onsen Hot Spring Resort Songgoriti</t>
+          <t>Bobocabin Coban Rondo, Malang</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1446507</v>
+        <v>813000</v>
       </c>
       <c r="E42" t="n">
-        <v>1446507</v>
+        <v>813000</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3398,17 +3398,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Warung Sate Gule Bang Tismanto</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>68500</v>
+        <v>60000</v>
       </c>
       <c r="K42" t="n">
-        <v>411000</v>
+        <v>360000</v>
       </c>
       <c r="L42" t="n">
-        <v>9.32</v>
+        <v>33.99</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3416,16 +3416,16 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>20971</v>
+        <v>76482</v>
       </c>
       <c r="O42" t="n">
-        <v>1982978</v>
+        <v>1353982</v>
       </c>
       <c r="P42" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q42" t="n">
-        <v>17022</v>
+        <v>146018</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -3447,14 +3447,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>The Onsen Hot Spring Resort Songgoriti</t>
+          <t>Bobocabin Coban Rondo, Malang</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1446507</v>
+        <v>813000</v>
       </c>
       <c r="E43" t="n">
-        <v>1446507</v>
+        <v>813000</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3469,17 +3469,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Kutaraja Boutique Restaurant</t>
+          <t>DAPUR LAWAS MALANG</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>53500</v>
+        <v>58500</v>
       </c>
       <c r="K43" t="n">
-        <v>321000</v>
+        <v>351000</v>
       </c>
       <c r="L43" t="n">
-        <v>16.79</v>
+        <v>46.28</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3487,16 +3487,16 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>37772</v>
+        <v>104139</v>
       </c>
       <c r="O43" t="n">
-        <v>1909779</v>
+        <v>1372639</v>
       </c>
       <c r="P43" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q43" t="n">
-        <v>90221</v>
+        <v>127361</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3518,14 +3518,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>The Onsen Hot Spring Resort Songgoriti</t>
+          <t>Bobocabin Coban Rondo, Malang</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1446507</v>
+        <v>813000</v>
       </c>
       <c r="E44" t="n">
-        <v>1446507</v>
+        <v>813000</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3540,17 +3540,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Warung Sate Gule Bang Tismanto</t>
+          <t>Depot Widari</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>60000</v>
+        <v>50600</v>
       </c>
       <c r="K44" t="n">
-        <v>360000</v>
+        <v>303600</v>
       </c>
       <c r="L44" t="n">
-        <v>32.61</v>
+        <v>49.12</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3558,16 +3558,16 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>73363</v>
+        <v>110531</v>
       </c>
       <c r="O44" t="n">
-        <v>1984370</v>
+        <v>1331631</v>
       </c>
       <c r="P44" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q44" t="n">
-        <v>15630</v>
+        <v>168369</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -3589,14 +3589,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>The Onsen Hot Spring Resort Songgoriti</t>
+          <t>Bobocabin Coban Rondo, Malang</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1446507</v>
+        <v>813000</v>
       </c>
       <c r="E45" t="n">
-        <v>1446507</v>
+        <v>813000</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3611,17 +3611,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>DAPUR LAWAS MALANG</t>
+          <t>Depot Kanton</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>58500</v>
+        <v>65000</v>
       </c>
       <c r="K45" t="n">
-        <v>351000</v>
+        <v>390000</v>
       </c>
       <c r="L45" t="n">
-        <v>43.48</v>
+        <v>49.35</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -3629,16 +3629,16 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>97830</v>
+        <v>111039</v>
       </c>
       <c r="O45" t="n">
-        <v>1999837</v>
+        <v>1418539</v>
       </c>
       <c r="P45" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q45" t="n">
-        <v>163</v>
+        <v>81461</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -3660,14 +3660,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>The Onsen Hot Spring Resort Songgoriti</t>
+          <t>Bobocabin Coban Rondo, Malang</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1446507</v>
+        <v>813000</v>
       </c>
       <c r="E46" t="n">
-        <v>1446507</v>
+        <v>813000</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3682,17 +3682,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Depot Widari</t>
+          <t>Veggie Kitchen Malang (Vegetarian Food)</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>50600</v>
+        <v>55377</v>
       </c>
       <c r="K46" t="n">
-        <v>303600</v>
+        <v>332262</v>
       </c>
       <c r="L46" t="n">
-        <v>47.07</v>
+        <v>49.81</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -3700,16 +3700,16 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>105912</v>
+        <v>112063</v>
       </c>
       <c r="O46" t="n">
-        <v>1960519</v>
+        <v>1361825</v>
       </c>
       <c r="P46" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q46" t="n">
-        <v>39481</v>
+        <v>138175</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>

--- a/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket_destination.xlsx
+++ b/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket_destination.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,80 +457,105 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Wilayah Hotel</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Nama Wisata</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Harga Wisata (Satuan)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Total Biaya Wisata</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Wilayah Wisata</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Nama Kuliner Pagi</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Harga Kuliner Pagi</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Nama Kuliner Siang</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Harga Kuliner Siang</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Nama Kuliner Malam</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Harga Kuliner Malam</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Total Biaya Kuliner</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Wilayah Kuliner</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Rute Transport (Jarak km)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Armada Transport</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Biaya Transport</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Estimasi Total Biaya</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Total Budget Input</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Sisa Anggaran</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Kelebihan Anggaran</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -558,58 +583,81 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>104500</v>
-      </c>
       <c r="H2" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Sitangsu Cafe</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+        <v>104500</v>
+      </c>
+      <c r="I2" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Warung Djitoe</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>27000</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>26000</v>
       </c>
-      <c r="M2" t="n">
-        <v>132000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>52.98</v>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>26000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>131000</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P2" t="n">
-        <v>119204</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>599704</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
+        <v>35245</v>
+      </c>
+      <c r="V2" t="n">
+        <v>489745</v>
+      </c>
+      <c r="W2" t="n">
         <v>1500000</v>
       </c>
-      <c r="S2" t="n">
-        <v>900296</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>1010255</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -637,58 +685,81 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>104500</v>
-      </c>
       <c r="H3" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I3" t="inlineStr">
+        <v>104500</v>
+      </c>
+      <c r="I3" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Warung Djitoe</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>27000</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>26000</v>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>26000</v>
       </c>
-      <c r="M3" t="n">
-        <v>132000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="n">
+        <v>131000</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>119204</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>599704</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
+        <v>37963</v>
+      </c>
+      <c r="V3" t="n">
+        <v>492463</v>
+      </c>
+      <c r="W3" t="n">
         <v>1500000</v>
       </c>
-      <c r="S3" t="n">
-        <v>900296</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="n">
+        <v>1007537</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -716,58 +787,81 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>104500</v>
-      </c>
       <c r="H4" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Depot Indah Jaya</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>27000</v>
+        <v>104500</v>
+      </c>
+      <c r="I4" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Warung Pecel Madiun Amin 2</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="L4" t="n">
         <v>26000</v>
       </c>
-      <c r="M4" t="n">
-        <v>132000</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Warung Djitoe</t>
+        </is>
       </c>
       <c r="N4" t="n">
-        <v>52.98</v>
+        <v>27000</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>Warung Pecel Madiun Amin 2</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>26000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>131000</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P4" t="n">
-        <v>119204</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>599704</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
+        <v>41723</v>
+      </c>
+      <c r="V4" t="n">
+        <v>496223</v>
+      </c>
+      <c r="W4" t="n">
         <v>1500000</v>
       </c>
-      <c r="S4" t="n">
-        <v>900296</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="n">
+        <v>1003777</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -784,69 +878,92 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Batuque Town Villa 2</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="E5" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>104500</v>
-      </c>
       <c r="H5" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Mandhi Pagi Jual Nasi Goreng Kebuli, Briyani Nampan &amp; Mandhi | Spesialist Arabic Plating Tercantik SeMalang Raya</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+        <v>104500</v>
+      </c>
+      <c r="I5" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Warung Djitoe</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>27000</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>26000</v>
       </c>
-      <c r="M5" t="n">
-        <v>132000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>52.98</v>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>26000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>131000</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P5" t="n">
-        <v>119204</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>599704</v>
-      </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
+        <v>41994</v>
+      </c>
+      <c r="V5" t="n">
+        <v>495676</v>
+      </c>
+      <c r="W5" t="n">
         <v>1500000</v>
       </c>
-      <c r="S5" t="n">
-        <v>900296</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="X5" t="n">
+        <v>1004324</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -863,69 +980,92 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Batuque Town Villa 2</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="E6" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>104500</v>
-      </c>
       <c r="H6" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Depot Surya</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+        <v>104500</v>
+      </c>
+      <c r="I6" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Warung Djitoe</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>27000</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>26000</v>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="P6" t="n">
         <v>26000</v>
       </c>
-      <c r="M6" t="n">
-        <v>132000</v>
-      </c>
-      <c r="N6" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="n">
+        <v>131000</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P6" t="n">
-        <v>119204</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>599704</v>
-      </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
+        <v>44712</v>
+      </c>
+      <c r="V6" t="n">
+        <v>498394</v>
+      </c>
+      <c r="W6" t="n">
         <v>1500000</v>
       </c>
-      <c r="S6" t="n">
-        <v>900296</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="X6" t="n">
+        <v>1001606</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -942,69 +1082,92 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Batuque Town Villa 2</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="E7" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>104500</v>
-      </c>
       <c r="H7" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Waroeng Dhuro</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>26800</v>
+        <v>104500</v>
+      </c>
+      <c r="I7" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Warung Pecel Madiun Amin 2</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="L7" t="n">
         <v>26000</v>
       </c>
-      <c r="M7" t="n">
-        <v>132000</v>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Warung Djitoe</t>
+        </is>
       </c>
       <c r="N7" t="n">
-        <v>52.98</v>
+        <v>27000</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>Warung Pecel Madiun Amin 2</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>26000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>131000</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P7" t="n">
-        <v>119204</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>599704</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
+        <v>46678</v>
+      </c>
+      <c r="V7" t="n">
+        <v>500360</v>
+      </c>
+      <c r="W7" t="n">
         <v>1500000</v>
       </c>
-      <c r="S7" t="n">
-        <v>900296</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="X7" t="n">
+        <v>999640</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1021,69 +1184,92 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Rosetta Villa &amp; Homestay</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="E8" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>104500</v>
-      </c>
       <c r="H8" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Warung "MANTAB" spesial Ayam Goreng Laos</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>26750</v>
+        <v>104500</v>
+      </c>
+      <c r="I8" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>Sitangsu Cafe</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>27000</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>26000</v>
       </c>
-      <c r="M8" t="n">
-        <v>132000</v>
-      </c>
-      <c r="N8" t="n">
-        <v>52.98</v>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>26000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>131000</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>119204</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>599704</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
+        <v>49454</v>
+      </c>
+      <c r="V8" t="n">
+        <v>499954</v>
+      </c>
+      <c r="W8" t="n">
         <v>1500000</v>
       </c>
-      <c r="S8" t="n">
-        <v>900296</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="X8" t="n">
+        <v>1000046</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1100,69 +1286,92 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Rosetta Villa &amp; Homestay</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="E9" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>104500</v>
-      </c>
       <c r="H9" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Kedai Pakcik Abin - Melayu Food &amp; Drink</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>26675</v>
+        <v>104500</v>
+      </c>
+      <c r="I9" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Warung Pecel Madiun Amin 2</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="L9" t="n">
         <v>26000</v>
       </c>
-      <c r="M9" t="n">
-        <v>132000</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Warung Djitoe</t>
+        </is>
       </c>
       <c r="N9" t="n">
-        <v>52.98</v>
+        <v>27000</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>Warung Pecel Madiun Amin 2</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>26000</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>131000</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>119204</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>599704</v>
-      </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
+        <v>49746</v>
+      </c>
+      <c r="V9" t="n">
+        <v>500246</v>
+      </c>
+      <c r="W9" t="n">
         <v>1500000</v>
       </c>
-      <c r="S9" t="n">
-        <v>900296</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="X9" t="n">
+        <v>999754</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1190,58 +1399,81 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>104500</v>
-      </c>
       <c r="H10" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Bebek Kerto tunggulwulung</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>26125</v>
+        <v>104500</v>
+      </c>
+      <c r="I10" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Warung Pecel Madiun Amin 2</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="L10" t="n">
         <v>26000</v>
       </c>
-      <c r="M10" t="n">
-        <v>132000</v>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Sitangsu Cafe</t>
+        </is>
       </c>
       <c r="N10" t="n">
-        <v>52.98</v>
+        <v>27000</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>Warung Pecel Madiun Amin 2</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>26000</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>131000</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P10" t="n">
-        <v>119204</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>599704</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="U10" t="n">
+        <v>50403</v>
+      </c>
+      <c r="V10" t="n">
+        <v>504903</v>
+      </c>
+      <c r="W10" t="n">
         <v>1500000</v>
       </c>
-      <c r="S10" t="n">
-        <v>900296</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="X10" t="n">
+        <v>995097</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1258,69 +1490,92 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Rosetta Villa &amp; Homestay</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="E11" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>104500</v>
-      </c>
       <c r="H11" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Mr. Mac Resto</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>26050</v>
+        <v>104500</v>
+      </c>
+      <c r="I11" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>Sitangsu Cafe</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>27000</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>26000</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="P11" t="n">
         <v>26000</v>
       </c>
-      <c r="M11" t="n">
-        <v>132000</v>
-      </c>
-      <c r="N11" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="Q11" t="n">
+        <v>131000</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P11" t="n">
-        <v>119204</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>599704</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
+        <v>52172</v>
+      </c>
+      <c r="V11" t="n">
+        <v>502672</v>
+      </c>
+      <c r="W11" t="n">
         <v>1500000</v>
       </c>
-      <c r="S11" t="n">
-        <v>900296</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="X11" t="n">
+        <v>997328</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1337,69 +1592,92 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Rosetta Villa &amp; Homestay</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="E12" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>104500</v>
-      </c>
       <c r="H12" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I12" t="inlineStr">
+        <v>104500</v>
+      </c>
+      <c r="I12" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Depot Shun Jaya Putra</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>26000</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
       <c r="L12" t="n">
         <v>26000</v>
       </c>
-      <c r="M12" t="n">
-        <v>132000</v>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Sitangsu Cafe</t>
+        </is>
       </c>
       <c r="N12" t="n">
-        <v>52.98</v>
+        <v>27000</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
+          <t>Warung Pecel Madiun Amin 2</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>26000</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>131000</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>23.73</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P12" t="n">
-        <v>119204</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>599704</v>
-      </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
+        <v>53385</v>
+      </c>
+      <c r="V12" t="n">
+        <v>503885</v>
+      </c>
+      <c r="W12" t="n">
         <v>1500000</v>
       </c>
-      <c r="S12" t="n">
-        <v>900296</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="X12" t="n">
+        <v>996115</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1416,33 +1694,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Batuque Town Villa 2</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="E13" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>104500</v>
-      </c>
       <c r="H13" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Warung Pecel Madiun Amin 2</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>26000</v>
+        <v>104500</v>
+      </c>
+      <c r="I13" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1452,33 +1732,54 @@
       <c r="L13" t="n">
         <v>26000</v>
       </c>
-      <c r="M13" t="n">
-        <v>132000</v>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Sitangsu Cafe</t>
+        </is>
       </c>
       <c r="N13" t="n">
-        <v>52.98</v>
+        <v>27000</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>Warung Pecel Madiun Amin 2</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>26000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>131000</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P13" t="n">
-        <v>119204</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>599704</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
+        <v>54307</v>
+      </c>
+      <c r="V13" t="n">
+        <v>507989</v>
+      </c>
+      <c r="W13" t="n">
         <v>1500000</v>
       </c>
-      <c r="S13" t="n">
-        <v>900296</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="X13" t="n">
+        <v>992011</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1495,69 +1796,92 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Family Homestay Arya</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>219000</v>
+        <v>220925</v>
       </c>
       <c r="E14" t="n">
-        <v>219000</v>
+        <v>220925</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>104500</v>
-      </c>
       <c r="H14" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Bahagia Family Cafe &amp; Pool</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
+        <v>104500</v>
+      </c>
+      <c r="I14" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Warung Djitoe</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>27000</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Warung Pecel Madiun Amin 2</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
         <v>26000</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Warung Pecel Madiun Amin 2</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
         <v>26000</v>
       </c>
-      <c r="M14" t="n">
-        <v>132000</v>
-      </c>
-      <c r="N14" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="Q14" t="n">
+        <v>131000</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P14" t="n">
-        <v>119204</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>599704</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
+        <v>57875</v>
+      </c>
+      <c r="V14" t="n">
+        <v>514300</v>
+      </c>
+      <c r="W14" t="n">
         <v>1500000</v>
       </c>
-      <c r="S14" t="n">
-        <v>900296</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="inlineStr">
+      <c r="X14" t="n">
+        <v>985700</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1574,69 +1898,92 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Family Homestay Arya</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>219000</v>
+        <v>220925</v>
       </c>
       <c r="E15" t="n">
-        <v>219000</v>
+        <v>220925</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>104500</v>
-      </c>
       <c r="H15" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Depot Manado Prilia Malang</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
+        <v>104500</v>
+      </c>
+      <c r="I15" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Warung Djitoe</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>27000</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
         <v>26000</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="P15" t="n">
         <v>26000</v>
       </c>
-      <c r="M15" t="n">
-        <v>132000</v>
-      </c>
-      <c r="N15" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="Q15" t="n">
+        <v>131000</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P15" t="n">
-        <v>119204</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>599704</v>
-      </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
+        <v>60593</v>
+      </c>
+      <c r="V15" t="n">
+        <v>517018</v>
+      </c>
+      <c r="W15" t="n">
         <v>1500000</v>
       </c>
-      <c r="S15" t="n">
-        <v>900296</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="inlineStr">
+      <c r="X15" t="n">
+        <v>982982</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1653,69 +2000,92 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Family Homestay Arya</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>219000</v>
+        <v>220925</v>
       </c>
       <c r="E16" t="n">
-        <v>219000</v>
+        <v>220925</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>104500</v>
-      </c>
       <c r="H16" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Ayam Geprek Dapur GSI</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>25781</v>
+        <v>104500</v>
+      </c>
+      <c r="I16" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Warung Pecel Madiun Amin 2</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="L16" t="n">
         <v>26000</v>
       </c>
-      <c r="M16" t="n">
-        <v>132000</v>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Warung Djitoe</t>
+        </is>
       </c>
       <c r="N16" t="n">
-        <v>52.98</v>
+        <v>27000</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
+          <t>Warung Pecel Madiun Amin 2</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>26000</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>131000</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P16" t="n">
-        <v>119204</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>599704</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="U16" t="n">
+        <v>63545</v>
+      </c>
+      <c r="V16" t="n">
+        <v>519970</v>
+      </c>
+      <c r="W16" t="n">
         <v>1500000</v>
       </c>
-      <c r="S16" t="n">
-        <v>900296</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="n">
+        <v>980030</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1732,33 +2102,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Sea Villa Kota Batu</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="E17" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>104500</v>
-      </c>
       <c r="H17" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Depot 59</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>95000</v>
+        <v>104500</v>
+      </c>
+      <c r="I17" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1768,33 +2140,54 @@
       <c r="L17" t="n">
         <v>51182</v>
       </c>
-      <c r="M17" t="n">
-        <v>329364</v>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Sop Janda Suroboyo - BATU MALANG</t>
+        </is>
       </c>
       <c r="N17" t="n">
-        <v>67.70999999999999</v>
+        <v>68500</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
+          <t>Kutaraja Boutique Restaurant</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>53500</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>277864</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P17" t="n">
-        <v>152339</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1424203</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
+        <v>50073</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1432437</v>
+      </c>
+      <c r="W17" t="n">
         <v>1500000</v>
       </c>
-      <c r="S17" t="n">
-        <v>75797</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="n">
+        <v>67563</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1811,69 +2204,92 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Sea Villa Kota Batu</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="E18" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>104500</v>
-      </c>
       <c r="H18" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>RJB - Rumah Jagal Bapa</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>90000</v>
+        <v>104500</v>
+      </c>
+      <c r="I18" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>Sop Janda Suroboyo - BATU MALANG</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>68500</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>De Bamboo Restaurant</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>51182</v>
       </c>
-      <c r="M18" t="n">
-        <v>329364</v>
-      </c>
-      <c r="N18" t="n">
-        <v>67.70999999999999</v>
-      </c>
       <c r="O18" t="inlineStr">
         <is>
+          <t>Kutaraja Boutique Restaurant</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>53500</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>295182</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>22.93</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P18" t="n">
-        <v>152339</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1424203</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="U18" t="n">
+        <v>51603</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1451285</v>
+      </c>
+      <c r="W18" t="n">
         <v>1500000</v>
       </c>
-      <c r="S18" t="n">
-        <v>75797</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="n">
+        <v>48715</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1890,33 +2306,35 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Sea Villa Kota Batu</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="E19" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>104500</v>
-      </c>
       <c r="H19" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>68500</v>
+        <v>104500</v>
+      </c>
+      <c r="I19" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1926,33 +2344,54 @@
       <c r="L19" t="n">
         <v>51182</v>
       </c>
-      <c r="M19" t="n">
-        <v>329364</v>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Kutaraja Boutique Restaurant</t>
+        </is>
       </c>
       <c r="N19" t="n">
-        <v>67.70999999999999</v>
+        <v>53500</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
+          <t>Sop Janda Suroboyo - BATU MALANG</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>68500</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>295182</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P19" t="n">
-        <v>152339</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1424203</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="U19" t="n">
+        <v>60071</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1459753</v>
+      </c>
+      <c r="W19" t="n">
         <v>1500000</v>
       </c>
-      <c r="S19" t="n">
-        <v>75797</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="n">
+        <v>40247</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1969,69 +2408,92 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Sea Villa Kota Batu</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="E20" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>104500</v>
-      </c>
       <c r="H20" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Depot Gang Djangkrik</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>65714</v>
+        <v>104500</v>
+      </c>
+      <c r="I20" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Sop Janda Suroboyo - BATU MALANG</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>51182</v>
-      </c>
-      <c r="M20" t="n">
-        <v>329364</v>
+        <v>68500</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Warung Sate Gule Bang Tismanto</t>
+        </is>
       </c>
       <c r="N20" t="n">
-        <v>67.70999999999999</v>
+        <v>60000</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>Kutaraja Boutique Restaurant</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>53500</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>304000</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P20" t="n">
-        <v>152339</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1424203</v>
-      </c>
-      <c r="R20" t="n">
+      <c r="U20" t="n">
+        <v>88856</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1497356</v>
+      </c>
+      <c r="W20" t="n">
         <v>1500000</v>
       </c>
-      <c r="S20" t="n">
-        <v>75797</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="n">
+        <v>2644</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2059,58 +2521,81 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>104500</v>
-      </c>
       <c r="H21" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Depot Kanton</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>65000</v>
+        <v>104500</v>
+      </c>
+      <c r="I21" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>Sop Janda Suroboyo - BATU MALANG</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>68500</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>De Bamboo Restaurant</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>51182</v>
       </c>
-      <c r="M21" t="n">
-        <v>329364</v>
-      </c>
-      <c r="N21" t="n">
-        <v>67.70999999999999</v>
-      </c>
       <c r="O21" t="inlineStr">
         <is>
+          <t>DEDUWA OLEH OLEH RESTO DAN TRANSIT</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>488182</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P21" t="n">
-        <v>152339</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1424203</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
+        <v>51358</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1457040</v>
+      </c>
+      <c r="W21" t="n">
         <v>1500000</v>
       </c>
-      <c r="S21" t="n">
-        <v>75797</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="n">
+        <v>42960</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2138,58 +2623,81 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>104500</v>
-      </c>
       <c r="H22" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Warung Sate Gule Bang Tismanto</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>60000</v>
+        <v>104500</v>
+      </c>
+      <c r="I22" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t>Sop Janda Suroboyo - BATU MALANG</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>68500</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>DEDUWA OLEH OLEH RESTO DAN TRANSIT</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>150000</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>De Bamboo Restaurant</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="P22" t="n">
         <v>51182</v>
       </c>
-      <c r="M22" t="n">
-        <v>329364</v>
-      </c>
-      <c r="N22" t="n">
-        <v>67.70999999999999</v>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="Q22" t="n">
+        <v>488182</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>22.93</v>
+      </c>
+      <c r="T22" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P22" t="n">
-        <v>152339</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1424203</v>
-      </c>
-      <c r="R22" t="n">
+      <c r="U22" t="n">
+        <v>51603</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1457285</v>
+      </c>
+      <c r="W22" t="n">
         <v>1500000</v>
       </c>
-      <c r="S22" t="n">
-        <v>75797</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="n">
+        <v>42715</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2217,22 +2725,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>104500</v>
-      </c>
       <c r="H23" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Depot 88 - Araya</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>58750</v>
+        <v>104500</v>
+      </c>
+      <c r="I23" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2242,33 +2752,54 @@
       <c r="L23" t="n">
         <v>51182</v>
       </c>
-      <c r="M23" t="n">
-        <v>329364</v>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Sop Janda Suroboyo - BATU MALANG</t>
+        </is>
       </c>
       <c r="N23" t="n">
-        <v>67.70999999999999</v>
+        <v>68500</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
+          <t>DEDUWA OLEH OLEH RESTO DAN TRANSIT</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>470864</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P23" t="n">
-        <v>152339</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1424203</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="U23" t="n">
+        <v>60664</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1449028</v>
+      </c>
+      <c r="W23" t="n">
         <v>1500000</v>
       </c>
-      <c r="S23" t="n">
-        <v>75797</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="n">
+        <v>50972</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2296,22 +2827,24 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>104500</v>
-      </c>
       <c r="H24" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>DAPUR LAWAS MALANG</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>58500</v>
+        <v>104500</v>
+      </c>
+      <c r="I24" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2321,33 +2854,54 @@
       <c r="L24" t="n">
         <v>51182</v>
       </c>
-      <c r="M24" t="n">
-        <v>329364</v>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Kutaraja Boutique Restaurant</t>
+        </is>
       </c>
       <c r="N24" t="n">
-        <v>67.70999999999999</v>
+        <v>53500</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
+          <t>DEDUWA OLEH OLEH RESTO DAN TRANSIT</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>473182</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>33.27</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P24" t="n">
-        <v>152339</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1424203</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="U24" t="n">
+        <v>74856</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1465538</v>
+      </c>
+      <c r="W24" t="n">
         <v>1500000</v>
       </c>
-      <c r="S24" t="n">
-        <v>75797</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="n">
+        <v>34462</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2364,69 +2918,92 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Chalet Bromo Restaurant and Lounge</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="E25" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>104500</v>
-      </c>
       <c r="H25" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Depot Sate Kambing Pak Di</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>56000</v>
+        <v>104500</v>
+      </c>
+      <c r="I25" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>51182</v>
-      </c>
-      <c r="M25" t="n">
-        <v>329364</v>
+        <v>55500</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Kutaraja Boutique Restaurant</t>
+        </is>
       </c>
       <c r="N25" t="n">
-        <v>67.70999999999999</v>
+        <v>53500</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
+          <t>Depot 88 - Araya</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>58750</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>282000</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>142.72</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P25" t="n">
-        <v>152339</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1424203</v>
-      </c>
-      <c r="R25" t="n">
+      <c r="U25" t="n">
+        <v>321114</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1451687</v>
+      </c>
+      <c r="W25" t="n">
         <v>1500000</v>
       </c>
-      <c r="S25" t="n">
-        <v>75797</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="n">
+        <v>48313</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2443,69 +3020,92 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Chalet Bromo Restaurant and Lounge</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="E26" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>104500</v>
-      </c>
       <c r="H26" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I26" t="inlineStr">
+        <v>104500</v>
+      </c>
+      <c r="I26" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>55500</v>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>De Bamboo Restaurant</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>51182</v>
-      </c>
-      <c r="M26" t="n">
-        <v>329364</v>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>DAPUR LAWAS MALANG</t>
+        </is>
       </c>
       <c r="N26" t="n">
-        <v>67.70999999999999</v>
+        <v>58500</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
+          <t>Depot 88 - Araya</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>58750</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>287000</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>142.85</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P26" t="n">
-        <v>152339</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1424203</v>
-      </c>
-      <c r="R26" t="n">
+      <c r="U26" t="n">
+        <v>321419</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1456992</v>
+      </c>
+      <c r="W26" t="n">
         <v>1500000</v>
       </c>
-      <c r="S26" t="n">
-        <v>75797</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="n">
+        <v>43008</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2522,69 +3122,92 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Chalet Bromo Restaurant and Lounge</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="E27" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>104500</v>
-      </c>
       <c r="H27" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Veggie Kitchen Malang (Vegetarian Food)</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>55377</v>
+        <v>104500</v>
+      </c>
+      <c r="I27" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>51182</v>
-      </c>
-      <c r="M27" t="n">
-        <v>329364</v>
+        <v>55500</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Sop Janda Suroboyo - BATU MALANG</t>
+        </is>
       </c>
       <c r="N27" t="n">
-        <v>67.70999999999999</v>
+        <v>68500</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
+          <t>Depot 88 - Araya</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>58750</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>297000</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>143.61</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P27" t="n">
-        <v>152339</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1424203</v>
-      </c>
-      <c r="R27" t="n">
+      <c r="U27" t="n">
+        <v>323112</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1468685</v>
+      </c>
+      <c r="W27" t="n">
         <v>1500000</v>
       </c>
-      <c r="S27" t="n">
-        <v>75797</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="n">
+        <v>31315</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2601,69 +3224,92 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Chalet Bromo Restaurant and Lounge</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="E28" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>104500</v>
-      </c>
       <c r="H28" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Kutaraja Boutique Restaurant</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>53500</v>
+        <v>104500</v>
+      </c>
+      <c r="I28" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>51182</v>
-      </c>
-      <c r="M28" t="n">
-        <v>329364</v>
+        <v>55500</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Depot Gang Djangkrik</t>
+        </is>
       </c>
       <c r="N28" t="n">
-        <v>67.70999999999999</v>
+        <v>65714</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
+          <t>Depot 88 - Araya</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>58750</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>294214</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>143.75</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P28" t="n">
-        <v>152339</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1424203</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="U28" t="n">
+        <v>323433</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1466220</v>
+      </c>
+      <c r="W28" t="n">
         <v>1500000</v>
       </c>
-      <c r="S28" t="n">
-        <v>75797</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="n">
+        <v>33780</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2680,69 +3326,92 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Chalet Bromo Restaurant and Lounge</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="E29" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>104500</v>
-      </c>
       <c r="H29" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>De Bamboo Restaurant</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>51182</v>
+        <v>104500</v>
+      </c>
+      <c r="I29" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>68500</v>
-      </c>
-      <c r="M29" t="n">
-        <v>329364</v>
+        <v>55500</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Depot Kanton</t>
+        </is>
       </c>
       <c r="N29" t="n">
-        <v>67.70999999999999</v>
+        <v>65000</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
+          <t>Depot 88 - Araya</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>58750</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>293500</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P29" t="n">
-        <v>152339</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1424203</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="U29" t="n">
+        <v>326218</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1468291</v>
+      </c>
+      <c r="W29" t="n">
         <v>1500000</v>
       </c>
-      <c r="S29" t="n">
-        <v>75797</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="n">
+        <v>31709</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2759,69 +3428,92 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Chalet Bromo Restaurant and Lounge</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="E30" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>104500</v>
-      </c>
       <c r="H30" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Depot Widari</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>50600</v>
+        <v>104500</v>
+      </c>
+      <c r="I30" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>51182</v>
-      </c>
-      <c r="M30" t="n">
-        <v>329364</v>
+        <v>55500</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>RJB - Rumah Jagal Bapa</t>
+        </is>
       </c>
       <c r="N30" t="n">
-        <v>67.70999999999999</v>
+        <v>90000</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
+          <t>Depot 88 - Araya</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>58750</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>318500</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>145.53</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P30" t="n">
-        <v>152339</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1424203</v>
-      </c>
-      <c r="R30" t="n">
+      <c r="U30" t="n">
+        <v>327448</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1494521</v>
+      </c>
+      <c r="W30" t="n">
         <v>1500000</v>
       </c>
-      <c r="S30" t="n">
-        <v>75797</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="n">
+        <v>5479</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2838,69 +3530,92 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Chalet Bromo Restaurant and Lounge</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="E31" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>Museum Angkut</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>104500</v>
-      </c>
       <c r="H31" t="n">
-        <v>129500</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Warung Nasi Widuri</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
+        <v>104500</v>
+      </c>
+      <c r="I31" t="n">
+        <v>104500</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>55500</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Depot Widari</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
         <v>50600</v>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>De Bamboo Restaurant</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>51182</v>
-      </c>
-      <c r="M31" t="n">
-        <v>329364</v>
-      </c>
-      <c r="N31" t="n">
-        <v>67.70999999999999</v>
-      </c>
       <c r="O31" t="inlineStr">
         <is>
+          <t>Depot 88 - Araya</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>58750</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>279100</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>146.03</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P31" t="n">
-        <v>152339</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1424203</v>
-      </c>
-      <c r="R31" t="n">
+      <c r="U31" t="n">
+        <v>328567</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1456240</v>
+      </c>
+      <c r="W31" t="n">
         <v>1500000</v>
       </c>
-      <c r="S31" t="n">
-        <v>75797</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="n">
+        <v>43760</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -3257,137 +3972,137 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Batuque Town Villa 2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Batuque Town Villa 2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Batuque Town Villa 2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Rosetta Villa &amp; Homestay</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Rosetta Villa &amp; Homestay</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>Hotel Prima Asri 153</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Hotel Prima Asri 153</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Hotel Prima Asri 153</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Hotel Prima Asri 153</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Hotel Prima Asri 153</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Hotel Prima Asri 153</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Rosetta Villa &amp; Homestay</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Rosetta Villa &amp; Homestay</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Batuque Town Villa 2</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Family Homestay Arya</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Family Homestay Arya</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Family Homestay Arya</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>Sea Villa Kota Batu</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Sea Villa Kota Batu</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Sea Villa Kota Batu</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sea Villa Kota Batu</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>Bobocabin Coban Rondo, Malang</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Bobocabin Coban Rondo, Malang</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Bobocabin Coban Rondo, Malang</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Bobocabin Coban Rondo, Malang</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Chalet Bromo Restaurant and Lounge</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Chalet Bromo Restaurant and Lounge</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Chalet Bromo Restaurant and Lounge</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Chalet Bromo Restaurant and Lounge</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Chalet Bromo Restaurant and Lounge</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Chalet Bromo Restaurant and Lounge</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
+          <t>Chalet Bromo Restaurant and Lounge</t>
         </is>
       </c>
     </row>
@@ -3407,52 +4122,52 @@
         <v>219000</v>
       </c>
       <c r="E4" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="F4" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="G4" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="H4" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="I4" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="J4" t="n">
         <v>219000</v>
       </c>
       <c r="K4" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="L4" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="M4" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="N4" t="n">
-        <v>219000</v>
+        <v>220925</v>
       </c>
       <c r="O4" t="n">
-        <v>219000</v>
+        <v>220925</v>
       </c>
       <c r="P4" t="n">
-        <v>219000</v>
+        <v>220925</v>
       </c>
       <c r="Q4" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="R4" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="S4" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="T4" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="U4" t="n">
         <v>813000</v>
@@ -3467,25 +4182,25 @@
         <v>813000</v>
       </c>
       <c r="Y4" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="Z4" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="AA4" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="AB4" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="AC4" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="AD4" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="AE4" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
     </row>
     <row r="5">
@@ -3750,152 +4465,152 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Warung Djitoe</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Warung Djitoe</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Warung Djitoe</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Warung Djitoe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sitangsu Cafe</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Sitangsu Cafe</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Warung Djitoe</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Warung Djitoe</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Depot Shun Jaya Putra</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Depot Shun Jaya Putra</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Depot Shun Jaya Putra</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Depot Shun Jaya Putra</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Depot Shun Jaya Putra</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Depot Shun Jaya Putra</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Depot Shun Jaya Putra</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Depot Shun Jaya Putra</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>De Bamboo Restaurant</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>Sop Janda Suroboyo - BATU MALANG</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>De Bamboo Restaurant</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>Sop Janda Suroboyo - BATU MALANG</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Sop Janda Suroboyo - BATU MALANG</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Sop Janda Suroboyo - BATU MALANG</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
-        </is>
-      </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>De Bamboo Restaurant</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>De Bamboo Restaurant</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
     </row>
@@ -3906,25 +4621,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="C8" t="n">
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="D8" t="n">
         <v>26000</v>
       </c>
       <c r="E8" t="n">
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="F8" t="n">
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="G8" t="n">
         <v>26000</v>
       </c>
       <c r="H8" t="n">
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="I8" t="n">
         <v>26000</v>
@@ -3933,7 +4648,7 @@
         <v>26000</v>
       </c>
       <c r="K8" t="n">
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="L8" t="n">
         <v>26000</v>
@@ -3942,22 +4657,22 @@
         <v>26000</v>
       </c>
       <c r="N8" t="n">
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="O8" t="n">
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="P8" t="n">
         <v>26000</v>
       </c>
       <c r="Q8" t="n">
-        <v>68500</v>
+        <v>51182</v>
       </c>
       <c r="R8" t="n">
         <v>68500</v>
       </c>
       <c r="S8" t="n">
-        <v>68500</v>
+        <v>51182</v>
       </c>
       <c r="T8" t="n">
         <v>68500</v>
@@ -3969,31 +4684,31 @@
         <v>68500</v>
       </c>
       <c r="W8" t="n">
-        <v>68500</v>
+        <v>51182</v>
       </c>
       <c r="X8" t="n">
-        <v>68500</v>
+        <v>51182</v>
       </c>
       <c r="Y8" t="n">
-        <v>68500</v>
+        <v>55500</v>
       </c>
       <c r="Z8" t="n">
-        <v>68500</v>
+        <v>55500</v>
       </c>
       <c r="AA8" t="n">
-        <v>68500</v>
+        <v>55500</v>
       </c>
       <c r="AB8" t="n">
-        <v>68500</v>
+        <v>55500</v>
       </c>
       <c r="AC8" t="n">
-        <v>68500</v>
+        <v>55500</v>
       </c>
       <c r="AD8" t="n">
-        <v>68500</v>
+        <v>55500</v>
       </c>
       <c r="AE8" t="n">
-        <v>68500</v>
+        <v>55500</v>
       </c>
     </row>
     <row r="9">
@@ -4004,152 +4719,152 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Warung Pecel Madiun Amin 2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Warung Djitoe</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Warung Pecel Madiun Amin 2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Warung Djitoe</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Warung Pecel Madiun Amin 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Warung Djitoe</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sitangsu Cafe</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Sitangsu Cafe</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Sitangsu Cafe</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Warung Pecel Madiun Amin 2</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Warung Djitoe</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Warung Djitoe</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Warung Djitoe</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Warung Djitoe</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Warung Djitoe</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Warung Djitoe</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Warung Djitoe</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Warung Djitoe</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Warung Djitoe</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Warung Djitoe</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Warung Djitoe</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Warung Djitoe</t>
-        </is>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>Sop Janda Suroboyo - BATU MALANG</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>De Bamboo Restaurant</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Kutaraja Boutique Restaurant</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Warung Sate Gule Bang Tismanto</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>De Bamboo Restaurant</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>DEDUWA OLEH OLEH RESTO DAN TRANSIT</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sop Janda Suroboyo - BATU MALANG</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Kutaraja Boutique Restaurant</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Kutaraja Boutique Restaurant</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>DAPUR LAWAS MALANG</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Sop Janda Suroboyo - BATU MALANG</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Depot Gang Djangkrik</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Depot Kanton</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
           <t>RJB - Rumah Jagal Bapa</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>RJB - Rumah Jagal Bapa</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>RJB - Rumah Jagal Bapa</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>RJB - Rumah Jagal Bapa</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>RJB - Rumah Jagal Bapa</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>RJB - Rumah Jagal Bapa</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>RJB - Rumah Jagal Bapa</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>RJB - Rumah Jagal Bapa</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>RJB - Rumah Jagal Bapa</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>RJB - Rumah Jagal Bapa</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>RJB - Rumah Jagal Bapa</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RJB - Rumah Jagal Bapa</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>RJB - Rumah Jagal Bapa</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>RJB - Rumah Jagal Bapa</t>
-        </is>
-      </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>RJB - Rumah Jagal Bapa</t>
+          <t>Depot Widari</t>
         </is>
       </c>
     </row>
@@ -4160,25 +4875,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="C10" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="D10" t="n">
         <v>27000</v>
       </c>
       <c r="E10" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="F10" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="G10" t="n">
         <v>27000</v>
       </c>
       <c r="H10" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="I10" t="n">
         <v>27000</v>
@@ -4187,7 +4902,7 @@
         <v>27000</v>
       </c>
       <c r="K10" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="L10" t="n">
         <v>27000</v>
@@ -4196,58 +4911,58 @@
         <v>27000</v>
       </c>
       <c r="N10" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="O10" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="P10" t="n">
         <v>27000</v>
       </c>
       <c r="Q10" t="n">
-        <v>90000</v>
+        <v>68500</v>
       </c>
       <c r="R10" t="n">
-        <v>90000</v>
+        <v>51182</v>
       </c>
       <c r="S10" t="n">
-        <v>90000</v>
+        <v>53500</v>
       </c>
       <c r="T10" t="n">
-        <v>90000</v>
+        <v>60000</v>
       </c>
       <c r="U10" t="n">
-        <v>90000</v>
+        <v>51182</v>
       </c>
       <c r="V10" t="n">
-        <v>90000</v>
+        <v>150000</v>
       </c>
       <c r="W10" t="n">
-        <v>90000</v>
+        <v>68500</v>
       </c>
       <c r="X10" t="n">
-        <v>90000</v>
+        <v>53500</v>
       </c>
       <c r="Y10" t="n">
-        <v>90000</v>
+        <v>53500</v>
       </c>
       <c r="Z10" t="n">
-        <v>90000</v>
+        <v>58500</v>
       </c>
       <c r="AA10" t="n">
-        <v>90000</v>
+        <v>68500</v>
       </c>
       <c r="AB10" t="n">
-        <v>90000</v>
+        <v>65714</v>
       </c>
       <c r="AC10" t="n">
-        <v>90000</v>
+        <v>65000</v>
       </c>
       <c r="AD10" t="n">
         <v>90000</v>
       </c>
       <c r="AE10" t="n">
-        <v>90000</v>
+        <v>50600</v>
       </c>
     </row>
     <row r="11">
@@ -4258,152 +4973,152 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Warung Pecel Madiun Amin 2</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Warung Pecel Madiun Amin 2</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Warung Pecel Madiun Amin 2</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Warung Pecel Madiun Amin 2</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>Kutaraja Boutique Restaurant</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Kutaraja Boutique Restaurant</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Sop Janda Suroboyo - BATU MALANG</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kutaraja Boutique Restaurant</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>DEDUWA OLEH OLEH RESTO DAN TRANSIT</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>De Bamboo Restaurant</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>De Bamboo Restaurant</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>De Bamboo Restaurant</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>De Bamboo Restaurant</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>De Bamboo Restaurant</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>De Bamboo Restaurant</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>DEDUWA OLEH OLEH RESTO DAN TRANSIT</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>DEDUWA OLEH OLEH RESTO DAN TRANSIT</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot 88 - Araya</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot 88 - Araya</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot 88 - Araya</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot 88 - Araya</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot 88 - Araya</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot 88 - Araya</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot 88 - Araya</t>
         </is>
       </c>
     </row>
@@ -4459,49 +5174,49 @@
         <v>26000</v>
       </c>
       <c r="Q12" t="n">
-        <v>51182</v>
+        <v>53500</v>
       </c>
       <c r="R12" t="n">
-        <v>51182</v>
+        <v>53500</v>
       </c>
       <c r="S12" t="n">
-        <v>51182</v>
+        <v>68500</v>
       </c>
       <c r="T12" t="n">
-        <v>51182</v>
+        <v>53500</v>
       </c>
       <c r="U12" t="n">
-        <v>51182</v>
+        <v>150000</v>
       </c>
       <c r="V12" t="n">
         <v>51182</v>
       </c>
       <c r="W12" t="n">
-        <v>51182</v>
+        <v>150000</v>
       </c>
       <c r="X12" t="n">
-        <v>51182</v>
+        <v>150000</v>
       </c>
       <c r="Y12" t="n">
-        <v>51182</v>
+        <v>58750</v>
       </c>
       <c r="Z12" t="n">
-        <v>51182</v>
+        <v>58750</v>
       </c>
       <c r="AA12" t="n">
-        <v>51182</v>
+        <v>58750</v>
       </c>
       <c r="AB12" t="n">
-        <v>51182</v>
+        <v>58750</v>
       </c>
       <c r="AC12" t="n">
-        <v>51182</v>
+        <v>58750</v>
       </c>
       <c r="AD12" t="n">
-        <v>51182</v>
+        <v>58750</v>
       </c>
       <c r="AE12" t="n">
-        <v>51182</v>
+        <v>58750</v>
       </c>
     </row>
     <row r="13">
@@ -4520,52 +5235,52 @@
         <v>219000</v>
       </c>
       <c r="E13" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="F13" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="G13" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="H13" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="I13" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="J13" t="n">
         <v>219000</v>
       </c>
       <c r="K13" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="L13" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="M13" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="N13" t="n">
-        <v>219000</v>
+        <v>220925</v>
       </c>
       <c r="O13" t="n">
-        <v>219000</v>
+        <v>220925</v>
       </c>
       <c r="P13" t="n">
-        <v>219000</v>
+        <v>220925</v>
       </c>
       <c r="Q13" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="R13" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="S13" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="T13" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="U13" t="n">
         <v>813000</v>
@@ -4580,25 +5295,25 @@
         <v>813000</v>
       </c>
       <c r="Y13" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="Z13" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="AA13" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="AB13" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="AC13" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="AD13" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="AE13" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
     </row>
     <row r="14">
@@ -4750,49 +5465,49 @@
         <v>79000</v>
       </c>
       <c r="Q15" t="n">
-        <v>209682</v>
+        <v>173182</v>
       </c>
       <c r="R15" t="n">
-        <v>209682</v>
+        <v>173182</v>
       </c>
       <c r="S15" t="n">
-        <v>209682</v>
+        <v>173182</v>
       </c>
       <c r="T15" t="n">
-        <v>209682</v>
+        <v>182000</v>
       </c>
       <c r="U15" t="n">
-        <v>209682</v>
+        <v>269682</v>
       </c>
       <c r="V15" t="n">
-        <v>209682</v>
+        <v>269682</v>
       </c>
       <c r="W15" t="n">
-        <v>209682</v>
+        <v>269682</v>
       </c>
       <c r="X15" t="n">
-        <v>209682</v>
+        <v>254682</v>
       </c>
       <c r="Y15" t="n">
-        <v>209682</v>
+        <v>167750</v>
       </c>
       <c r="Z15" t="n">
-        <v>209682</v>
+        <v>172750</v>
       </c>
       <c r="AA15" t="n">
-        <v>209682</v>
+        <v>182750</v>
       </c>
       <c r="AB15" t="n">
-        <v>209682</v>
+        <v>179964</v>
       </c>
       <c r="AC15" t="n">
-        <v>209682</v>
+        <v>179250</v>
       </c>
       <c r="AD15" t="n">
-        <v>209682</v>
+        <v>204250</v>
       </c>
       <c r="AE15" t="n">
-        <v>209682</v>
+        <v>164850</v>
       </c>
     </row>
     <row r="16">
@@ -4802,94 +5517,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>59602</v>
+        <v>17622</v>
       </c>
       <c r="C16" t="n">
-        <v>59602</v>
+        <v>18982</v>
       </c>
       <c r="D16" t="n">
-        <v>59602</v>
+        <v>20862</v>
       </c>
       <c r="E16" t="n">
-        <v>59602</v>
+        <v>20997</v>
       </c>
       <c r="F16" t="n">
-        <v>59602</v>
+        <v>22356</v>
       </c>
       <c r="G16" t="n">
-        <v>59602</v>
+        <v>23339</v>
       </c>
       <c r="H16" t="n">
-        <v>59602</v>
+        <v>24727</v>
       </c>
       <c r="I16" t="n">
-        <v>59602</v>
+        <v>24873</v>
       </c>
       <c r="J16" t="n">
-        <v>59602</v>
+        <v>25202</v>
       </c>
       <c r="K16" t="n">
-        <v>59602</v>
+        <v>26086</v>
       </c>
       <c r="L16" t="n">
-        <v>59602</v>
+        <v>26692</v>
       </c>
       <c r="M16" t="n">
-        <v>59602</v>
+        <v>27154</v>
       </c>
       <c r="N16" t="n">
-        <v>59602</v>
+        <v>28938</v>
       </c>
       <c r="O16" t="n">
-        <v>59602</v>
+        <v>30296</v>
       </c>
       <c r="P16" t="n">
-        <v>59602</v>
+        <v>31772</v>
       </c>
       <c r="Q16" t="n">
-        <v>76170</v>
+        <v>25036</v>
       </c>
       <c r="R16" t="n">
-        <v>76170</v>
+        <v>25802</v>
       </c>
       <c r="S16" t="n">
-        <v>76170</v>
+        <v>30036</v>
       </c>
       <c r="T16" t="n">
-        <v>76170</v>
+        <v>44428</v>
       </c>
       <c r="U16" t="n">
-        <v>76170</v>
+        <v>25679</v>
       </c>
       <c r="V16" t="n">
-        <v>76170</v>
+        <v>25802</v>
       </c>
       <c r="W16" t="n">
-        <v>76170</v>
+        <v>30332</v>
       </c>
       <c r="X16" t="n">
-        <v>76170</v>
+        <v>37428</v>
       </c>
       <c r="Y16" t="n">
-        <v>76170</v>
+        <v>160557</v>
       </c>
       <c r="Z16" t="n">
-        <v>76170</v>
+        <v>160710</v>
       </c>
       <c r="AA16" t="n">
-        <v>76170</v>
+        <v>161556</v>
       </c>
       <c r="AB16" t="n">
-        <v>76170</v>
+        <v>161716</v>
       </c>
       <c r="AC16" t="n">
-        <v>76170</v>
+        <v>163109</v>
       </c>
       <c r="AD16" t="n">
-        <v>76170</v>
+        <v>163724</v>
       </c>
       <c r="AE16" t="n">
-        <v>76170</v>
+        <v>164284</v>
       </c>
     </row>
     <row r="17">
@@ -4899,25 +5614,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.21</v>
+        <v>4.56</v>
       </c>
       <c r="C17" t="n">
-        <v>2.21</v>
+        <v>4.56</v>
       </c>
       <c r="D17" t="n">
         <v>2.21</v>
       </c>
       <c r="E17" t="n">
-        <v>2.21</v>
+        <v>4.56</v>
       </c>
       <c r="F17" t="n">
-        <v>2.21</v>
+        <v>4.56</v>
       </c>
       <c r="G17" t="n">
         <v>2.21</v>
       </c>
       <c r="H17" t="n">
-        <v>2.21</v>
+        <v>6.28</v>
       </c>
       <c r="I17" t="n">
         <v>2.21</v>
@@ -4926,7 +5641,7 @@
         <v>2.21</v>
       </c>
       <c r="K17" t="n">
-        <v>2.21</v>
+        <v>6.28</v>
       </c>
       <c r="L17" t="n">
         <v>2.21</v>
@@ -4935,22 +5650,22 @@
         <v>2.21</v>
       </c>
       <c r="N17" t="n">
-        <v>2.21</v>
+        <v>4.56</v>
       </c>
       <c r="O17" t="n">
-        <v>2.21</v>
+        <v>4.56</v>
       </c>
       <c r="P17" t="n">
         <v>2.21</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.87</v>
+        <v>2.37</v>
       </c>
       <c r="R17" t="n">
         <v>1.87</v>
       </c>
       <c r="S17" t="n">
-        <v>1.87</v>
+        <v>2.37</v>
       </c>
       <c r="T17" t="n">
         <v>1.87</v>
@@ -4962,31 +5677,31 @@
         <v>1.87</v>
       </c>
       <c r="W17" t="n">
-        <v>1.87</v>
+        <v>2.37</v>
       </c>
       <c r="X17" t="n">
-        <v>1.87</v>
+        <v>2.37</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.87</v>
+        <v>23.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.87</v>
+        <v>23.16</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.87</v>
+        <v>23.16</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>23.16</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.87</v>
+        <v>23.16</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>23.16</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.87</v>
+        <v>23.16</v>
       </c>
     </row>
     <row r="18">
@@ -4996,94 +5711,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.56</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>4.56</v>
+        <v>2.21</v>
       </c>
       <c r="D18" t="n">
         <v>4.56</v>
       </c>
       <c r="E18" t="n">
-        <v>4.56</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>4.56</v>
+        <v>2.21</v>
       </c>
       <c r="G18" t="n">
         <v>4.56</v>
       </c>
       <c r="H18" t="n">
-        <v>4.56</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>4.56</v>
       </c>
       <c r="J18" t="n">
-        <v>4.56</v>
+        <v>6.28</v>
       </c>
       <c r="K18" t="n">
-        <v>4.56</v>
+        <v>2.21</v>
       </c>
       <c r="L18" t="n">
-        <v>4.56</v>
+        <v>6.28</v>
       </c>
       <c r="M18" t="n">
-        <v>4.56</v>
+        <v>6.28</v>
       </c>
       <c r="N18" t="n">
-        <v>4.56</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>4.56</v>
+        <v>2.21</v>
       </c>
       <c r="P18" t="n">
         <v>4.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>18.7</v>
+        <v>1.87</v>
       </c>
       <c r="R18" t="n">
-        <v>18.7</v>
+        <v>2.37</v>
       </c>
       <c r="S18" t="n">
-        <v>18.7</v>
+        <v>5.51</v>
       </c>
       <c r="T18" t="n">
-        <v>18.7</v>
+        <v>14.48</v>
       </c>
       <c r="U18" t="n">
-        <v>18.7</v>
+        <v>2.37</v>
       </c>
       <c r="V18" t="n">
-        <v>18.7</v>
+        <v>2.45</v>
       </c>
       <c r="W18" t="n">
-        <v>18.7</v>
+        <v>1.87</v>
       </c>
       <c r="X18" t="n">
-        <v>18.7</v>
+        <v>5.51</v>
       </c>
       <c r="Y18" t="n">
-        <v>18.7</v>
+        <v>5.51</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.7</v>
+        <v>20.52</v>
       </c>
       <c r="AA18" t="n">
-        <v>18.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB18" t="n">
-        <v>18.7</v>
+        <v>22.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>18.7</v>
+        <v>22.42</v>
       </c>
       <c r="AD18" t="n">
         <v>18.7</v>
       </c>
       <c r="AE18" t="n">
-        <v>18.7</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="19">
@@ -5093,94 +5808,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.38</v>
+        <v>1.83</v>
       </c>
       <c r="C19" t="n">
-        <v>4.38</v>
+        <v>2.27</v>
       </c>
       <c r="D19" t="n">
         <v>4.38</v>
       </c>
       <c r="E19" t="n">
-        <v>4.38</v>
+        <v>2.07</v>
       </c>
       <c r="F19" t="n">
-        <v>4.38</v>
+        <v>3.53</v>
       </c>
       <c r="G19" t="n">
-        <v>4.38</v>
+        <v>5.87</v>
       </c>
       <c r="H19" t="n">
-        <v>4.38</v>
+        <v>2.54</v>
       </c>
       <c r="I19" t="n">
-        <v>4.38</v>
+        <v>5.82</v>
       </c>
       <c r="J19" t="n">
-        <v>4.38</v>
+        <v>6.53</v>
       </c>
       <c r="K19" t="n">
-        <v>4.38</v>
+        <v>3.86</v>
       </c>
       <c r="L19" t="n">
-        <v>4.38</v>
+        <v>5.73</v>
       </c>
       <c r="M19" t="n">
-        <v>4.38</v>
+        <v>7.55</v>
       </c>
       <c r="N19" t="n">
-        <v>4.38</v>
+        <v>4.45</v>
       </c>
       <c r="O19" t="n">
-        <v>4.38</v>
+        <v>4.68</v>
       </c>
       <c r="P19" t="n">
-        <v>4.38</v>
+        <v>6.22</v>
       </c>
       <c r="Q19" t="n">
-        <v>23.41</v>
+        <v>4.27</v>
       </c>
       <c r="R19" t="n">
-        <v>23.41</v>
+        <v>6.43</v>
       </c>
       <c r="S19" t="n">
-        <v>23.41</v>
+        <v>1.97</v>
       </c>
       <c r="T19" t="n">
-        <v>23.41</v>
+        <v>10.88</v>
       </c>
       <c r="U19" t="n">
-        <v>23.41</v>
+        <v>3.94</v>
       </c>
       <c r="V19" t="n">
-        <v>23.41</v>
+        <v>3.91</v>
       </c>
       <c r="W19" t="n">
-        <v>23.41</v>
+        <v>6.59</v>
       </c>
       <c r="X19" t="n">
-        <v>23.41</v>
+        <v>10.75</v>
       </c>
       <c r="Y19" t="n">
-        <v>23.41</v>
+        <v>39.23</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.41</v>
+        <v>24.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.41</v>
+        <v>43.76</v>
       </c>
       <c r="AB19" t="n">
-        <v>23.41</v>
+        <v>22.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>23.41</v>
+        <v>24.59</v>
       </c>
       <c r="AD19" t="n">
-        <v>23.41</v>
+        <v>28.86</v>
       </c>
       <c r="AE19" t="n">
-        <v>23.41</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="20">
@@ -5190,7 +5905,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.83</v>
+        <v>2.27</v>
       </c>
       <c r="C20" t="n">
         <v>1.83</v>
@@ -5199,85 +5914,85 @@
         <v>1.83</v>
       </c>
       <c r="E20" t="n">
-        <v>1.83</v>
+        <v>3.53</v>
       </c>
       <c r="F20" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="G20" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="H20" t="n">
-        <v>1.83</v>
+        <v>3.86</v>
       </c>
       <c r="I20" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="J20" t="n">
         <v>1.83</v>
       </c>
       <c r="K20" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="L20" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="M20" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="N20" t="n">
-        <v>1.83</v>
+        <v>4.68</v>
       </c>
       <c r="O20" t="n">
-        <v>1.83</v>
+        <v>4.45</v>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>4.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.94</v>
+        <v>1.97</v>
       </c>
       <c r="R20" t="n">
-        <v>3.94</v>
+        <v>1.97</v>
       </c>
       <c r="S20" t="n">
-        <v>3.94</v>
+        <v>4.27</v>
       </c>
       <c r="T20" t="n">
-        <v>3.94</v>
+        <v>1.97</v>
       </c>
       <c r="U20" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="V20" t="n">
         <v>3.94</v>
       </c>
       <c r="W20" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="X20" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="AE20" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
     </row>
     <row r="21">
@@ -5287,7 +6002,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.83</v>
+        <v>2.27</v>
       </c>
       <c r="C21" t="n">
         <v>1.83</v>
@@ -5296,85 +6011,85 @@
         <v>1.83</v>
       </c>
       <c r="E21" t="n">
-        <v>1.83</v>
+        <v>3.53</v>
       </c>
       <c r="F21" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="G21" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="H21" t="n">
-        <v>1.83</v>
+        <v>3.86</v>
       </c>
       <c r="I21" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="J21" t="n">
         <v>1.83</v>
       </c>
       <c r="K21" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="L21" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="M21" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="N21" t="n">
-        <v>1.83</v>
+        <v>4.68</v>
       </c>
       <c r="O21" t="n">
-        <v>1.83</v>
+        <v>4.45</v>
       </c>
       <c r="P21" t="n">
-        <v>1.83</v>
+        <v>4.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.94</v>
+        <v>1.97</v>
       </c>
       <c r="R21" t="n">
-        <v>3.94</v>
+        <v>1.97</v>
       </c>
       <c r="S21" t="n">
-        <v>3.94</v>
+        <v>4.27</v>
       </c>
       <c r="T21" t="n">
-        <v>3.94</v>
+        <v>1.97</v>
       </c>
       <c r="U21" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="V21" t="n">
         <v>3.94</v>
       </c>
       <c r="W21" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="X21" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="AE21" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
     </row>
     <row r="22">
@@ -5384,94 +6099,94 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14.81</v>
+        <v>11.93</v>
       </c>
       <c r="C22" t="n">
-        <v>14.81</v>
+        <v>12.7</v>
       </c>
       <c r="D22" t="n">
         <v>14.81</v>
       </c>
       <c r="E22" t="n">
-        <v>14.81</v>
+        <v>14.69</v>
       </c>
       <c r="F22" t="n">
-        <v>14.81</v>
+        <v>14.44</v>
       </c>
       <c r="G22" t="n">
-        <v>14.81</v>
+        <v>16.78</v>
       </c>
       <c r="H22" t="n">
-        <v>14.81</v>
+        <v>17.54</v>
       </c>
       <c r="I22" t="n">
-        <v>14.81</v>
+        <v>17.67</v>
       </c>
       <c r="J22" t="n">
-        <v>14.81</v>
+        <v>18.67</v>
       </c>
       <c r="K22" t="n">
-        <v>14.81</v>
+        <v>17.42</v>
       </c>
       <c r="L22" t="n">
-        <v>14.81</v>
+        <v>19.28</v>
       </c>
       <c r="M22" t="n">
-        <v>14.81</v>
+        <v>20.17</v>
       </c>
       <c r="N22" t="n">
-        <v>14.81</v>
+        <v>19.37</v>
       </c>
       <c r="O22" t="n">
-        <v>14.81</v>
+        <v>20.35</v>
       </c>
       <c r="P22" t="n">
-        <v>14.81</v>
+        <v>21.89</v>
       </c>
       <c r="Q22" t="n">
-        <v>51.86</v>
+        <v>12.45</v>
       </c>
       <c r="R22" t="n">
-        <v>51.86</v>
+        <v>14.62</v>
       </c>
       <c r="S22" t="n">
-        <v>51.86</v>
+        <v>18.38</v>
       </c>
       <c r="T22" t="n">
-        <v>51.86</v>
+        <v>31.18</v>
       </c>
       <c r="U22" t="n">
-        <v>51.86</v>
+        <v>16</v>
       </c>
       <c r="V22" t="n">
-        <v>51.86</v>
+        <v>16.11</v>
       </c>
       <c r="W22" t="n">
-        <v>51.86</v>
+        <v>18.65</v>
       </c>
       <c r="X22" t="n">
-        <v>51.86</v>
+        <v>26.45</v>
       </c>
       <c r="Y22" t="n">
-        <v>51.86</v>
+        <v>107.93</v>
       </c>
       <c r="Z22" t="n">
-        <v>51.86</v>
+        <v>108.07</v>
       </c>
       <c r="AA22" t="n">
-        <v>51.86</v>
+        <v>108.82</v>
       </c>
       <c r="AB22" t="n">
-        <v>51.86</v>
+        <v>108.96</v>
       </c>
       <c r="AC22" t="n">
-        <v>51.86</v>
+        <v>110.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>51.86</v>
+        <v>110.75</v>
       </c>
       <c r="AE22" t="n">
-        <v>51.86</v>
+        <v>111.24</v>
       </c>
     </row>
     <row r="23">
@@ -5481,94 +6196,94 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>462102</v>
+        <v>420122</v>
       </c>
       <c r="C23" t="n">
-        <v>462102</v>
+        <v>421482</v>
       </c>
       <c r="D23" t="n">
-        <v>462102</v>
+        <v>423362</v>
       </c>
       <c r="E23" t="n">
-        <v>462102</v>
+        <v>422679</v>
       </c>
       <c r="F23" t="n">
-        <v>462102</v>
+        <v>424038</v>
       </c>
       <c r="G23" t="n">
-        <v>462102</v>
+        <v>425021</v>
       </c>
       <c r="H23" t="n">
-        <v>462102</v>
+        <v>423227</v>
       </c>
       <c r="I23" t="n">
-        <v>462102</v>
+        <v>423373</v>
       </c>
       <c r="J23" t="n">
-        <v>462102</v>
+        <v>427702</v>
       </c>
       <c r="K23" t="n">
-        <v>462102</v>
+        <v>424586</v>
       </c>
       <c r="L23" t="n">
-        <v>462102</v>
+        <v>425192</v>
       </c>
       <c r="M23" t="n">
-        <v>462102</v>
+        <v>428836</v>
       </c>
       <c r="N23" t="n">
-        <v>462102</v>
+        <v>433363</v>
       </c>
       <c r="O23" t="n">
-        <v>462102</v>
+        <v>434721</v>
       </c>
       <c r="P23" t="n">
-        <v>462102</v>
+        <v>436197</v>
       </c>
       <c r="Q23" t="n">
-        <v>1203352</v>
+        <v>1302718</v>
       </c>
       <c r="R23" t="n">
-        <v>1203352</v>
+        <v>1303484</v>
       </c>
       <c r="S23" t="n">
-        <v>1203352</v>
+        <v>1307718</v>
       </c>
       <c r="T23" t="n">
-        <v>1203352</v>
+        <v>1330928</v>
       </c>
       <c r="U23" t="n">
-        <v>1203352</v>
+        <v>1212861</v>
       </c>
       <c r="V23" t="n">
-        <v>1203352</v>
+        <v>1212984</v>
       </c>
       <c r="W23" t="n">
-        <v>1203352</v>
+        <v>1217514</v>
       </c>
       <c r="X23" t="n">
-        <v>1203352</v>
+        <v>1209610</v>
       </c>
       <c r="Y23" t="n">
-        <v>1203352</v>
+        <v>1176880</v>
       </c>
       <c r="Z23" t="n">
-        <v>1203352</v>
+        <v>1182033</v>
       </c>
       <c r="AA23" t="n">
-        <v>1203352</v>
+        <v>1192879</v>
       </c>
       <c r="AB23" t="n">
-        <v>1203352</v>
+        <v>1190253</v>
       </c>
       <c r="AC23" t="n">
-        <v>1203352</v>
+        <v>1190932</v>
       </c>
       <c r="AD23" t="n">
-        <v>1203352</v>
+        <v>1216547</v>
       </c>
       <c r="AE23" t="n">
-        <v>1203352</v>
+        <v>1177707</v>
       </c>
     </row>
     <row r="24">
@@ -5833,152 +6548,152 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kwan Im Tong (Guan Yin Dang) (Mahayana, Tridharma)</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Rest Area 84B Malang Strudel Playland</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Rest Area 84B Malang Strudel Playland</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Rest Area 84B Malang Strudel Playland</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Rest Area 84B Malang Strudel Playland</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Rest Area 84B Malang Strudel Playland</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Rest Area 84B Malang Strudel Playland</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Rest Area 84B Malang Strudel Playland</t>
         </is>
       </c>
     </row>
@@ -5989,94 +6704,94 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -6092,147 +6807,147 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Depot Shun Jaya Putra</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Warung Pecel Madiun Amin 2</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Warung Pecel Madiun Amin 2</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Warung Pecel Madiun Amin 2</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Warung Pecel Madiun Amin 2</t>
-        </is>
-      </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Kutaraja Boutique Restaurant</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Kutaraja Boutique Restaurant</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Kutaraja Boutique Restaurant</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Kutaraja Boutique Restaurant</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>DEDUWA OLEH OLEH RESTO DAN TRANSIT</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>DEDUWA OLEH OLEH RESTO DAN TRANSIT</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>DEDUWA OLEH OLEH RESTO DAN TRANSIT</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>DEDUWA OLEH OLEH RESTO DAN TRANSIT</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot 88 - Araya</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot 88 - Araya</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot 88 - Araya</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot 88 - Araya</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot 88 - Araya</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot 88 - Araya</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>Depot 88 - Araya</t>
         </is>
       </c>
     </row>
@@ -6288,49 +7003,49 @@
         <v>26000</v>
       </c>
       <c r="Q29" t="n">
-        <v>51182</v>
+        <v>53500</v>
       </c>
       <c r="R29" t="n">
-        <v>51182</v>
+        <v>53500</v>
       </c>
       <c r="S29" t="n">
-        <v>51182</v>
+        <v>53500</v>
       </c>
       <c r="T29" t="n">
-        <v>51182</v>
+        <v>53500</v>
       </c>
       <c r="U29" t="n">
-        <v>51182</v>
+        <v>150000</v>
       </c>
       <c r="V29" t="n">
-        <v>51182</v>
+        <v>150000</v>
       </c>
       <c r="W29" t="n">
-        <v>51182</v>
+        <v>150000</v>
       </c>
       <c r="X29" t="n">
-        <v>51182</v>
+        <v>150000</v>
       </c>
       <c r="Y29" t="n">
-        <v>51182</v>
+        <v>58750</v>
       </c>
       <c r="Z29" t="n">
-        <v>51182</v>
+        <v>58750</v>
       </c>
       <c r="AA29" t="n">
-        <v>51182</v>
+        <v>58750</v>
       </c>
       <c r="AB29" t="n">
-        <v>51182</v>
+        <v>58750</v>
       </c>
       <c r="AC29" t="n">
-        <v>51182</v>
+        <v>58750</v>
       </c>
       <c r="AD29" t="n">
-        <v>51182</v>
+        <v>58750</v>
       </c>
       <c r="AE29" t="n">
-        <v>51182</v>
+        <v>58750</v>
       </c>
     </row>
     <row r="30">
@@ -6341,152 +7056,152 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Depot Indah Jaya</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Depot Indah Jaya</t>
+          <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Depot Indah Jaya</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Depot Indah Jaya</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Depot Indah Jaya</t>
+          <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Depot Indah Jaya</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Depot Indah Jaya</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Depot Indah Jaya</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Depot Indah Jaya</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Depot Indah Jaya</t>
+          <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Depot Indah Jaya</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Depot Indah Jaya</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Depot Indah Jaya</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Depot Indah Jaya</t>
+          <t>Warung Pecel Madiun Amin 2</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Depot Indah Jaya</t>
+          <t>Depot Shun Jaya Putra</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
+          <t>De Bamboo Restaurant</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
           <t>Sop Janda Suroboyo - BATU MALANG</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>Sop Janda Suroboyo - BATU MALANG</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>Sop Janda Suroboyo - BATU MALANG</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Sop Janda Suroboyo - BATU MALANG</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Sop Janda Suroboyo - BATU MALANG</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>De Bamboo Restaurant</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
         <is>
           <t>Sop Janda Suroboyo - BATU MALANG</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
-        </is>
-      </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
         </is>
       </c>
     </row>
@@ -6497,52 +7212,52 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="C31" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="D31" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="E31" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="F31" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="G31" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="H31" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="I31" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="J31" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="K31" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="L31" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="M31" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="N31" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="O31" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="P31" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="Q31" t="n">
-        <v>68500</v>
+        <v>51182</v>
       </c>
       <c r="R31" t="n">
         <v>68500</v>
@@ -6560,31 +7275,31 @@
         <v>68500</v>
       </c>
       <c r="W31" t="n">
-        <v>68500</v>
+        <v>51182</v>
       </c>
       <c r="X31" t="n">
         <v>68500</v>
       </c>
       <c r="Y31" t="n">
-        <v>68500</v>
+        <v>55500</v>
       </c>
       <c r="Z31" t="n">
-        <v>68500</v>
+        <v>55500</v>
       </c>
       <c r="AA31" t="n">
-        <v>68500</v>
+        <v>55500</v>
       </c>
       <c r="AB31" t="n">
-        <v>68500</v>
+        <v>55500</v>
       </c>
       <c r="AC31" t="n">
-        <v>68500</v>
+        <v>55500</v>
       </c>
       <c r="AD31" t="n">
-        <v>68500</v>
+        <v>55500</v>
       </c>
       <c r="AE31" t="n">
-        <v>68500</v>
+        <v>55500</v>
       </c>
     </row>
     <row r="32">
@@ -6945,94 +7660,94 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -7042,94 +7757,94 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="C36" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="D36" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="E36" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="F36" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="G36" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="H36" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="I36" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="J36" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="K36" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="L36" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="M36" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="N36" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="O36" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="P36" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="Q36" t="n">
-        <v>119682</v>
+        <v>104682</v>
       </c>
       <c r="R36" t="n">
-        <v>119682</v>
+        <v>122000</v>
       </c>
       <c r="S36" t="n">
-        <v>119682</v>
+        <v>122000</v>
       </c>
       <c r="T36" t="n">
-        <v>119682</v>
+        <v>122000</v>
       </c>
       <c r="U36" t="n">
-        <v>119682</v>
+        <v>218500</v>
       </c>
       <c r="V36" t="n">
-        <v>119682</v>
+        <v>218500</v>
       </c>
       <c r="W36" t="n">
-        <v>119682</v>
+        <v>201182</v>
       </c>
       <c r="X36" t="n">
-        <v>119682</v>
+        <v>218500</v>
       </c>
       <c r="Y36" t="n">
-        <v>119682</v>
+        <v>114250</v>
       </c>
       <c r="Z36" t="n">
-        <v>119682</v>
+        <v>114250</v>
       </c>
       <c r="AA36" t="n">
-        <v>119682</v>
+        <v>114250</v>
       </c>
       <c r="AB36" t="n">
-        <v>119682</v>
+        <v>114250</v>
       </c>
       <c r="AC36" t="n">
-        <v>119682</v>
+        <v>114250</v>
       </c>
       <c r="AD36" t="n">
-        <v>119682</v>
+        <v>114250</v>
       </c>
       <c r="AE36" t="n">
-        <v>119682</v>
+        <v>114250</v>
       </c>
     </row>
     <row r="37">
@@ -7139,94 +7854,94 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>59602</v>
+        <v>17623</v>
       </c>
       <c r="C37" t="n">
-        <v>59602</v>
+        <v>18981</v>
       </c>
       <c r="D37" t="n">
-        <v>59602</v>
+        <v>20861</v>
       </c>
       <c r="E37" t="n">
-        <v>59602</v>
+        <v>20997</v>
       </c>
       <c r="F37" t="n">
-        <v>59602</v>
+        <v>22356</v>
       </c>
       <c r="G37" t="n">
-        <v>59602</v>
+        <v>23339</v>
       </c>
       <c r="H37" t="n">
-        <v>59602</v>
+        <v>24727</v>
       </c>
       <c r="I37" t="n">
-        <v>59602</v>
+        <v>24873</v>
       </c>
       <c r="J37" t="n">
-        <v>59602</v>
+        <v>25201</v>
       </c>
       <c r="K37" t="n">
-        <v>59602</v>
+        <v>26086</v>
       </c>
       <c r="L37" t="n">
-        <v>59602</v>
+        <v>26693</v>
       </c>
       <c r="M37" t="n">
-        <v>59602</v>
+        <v>27153</v>
       </c>
       <c r="N37" t="n">
-        <v>59602</v>
+        <v>28937</v>
       </c>
       <c r="O37" t="n">
-        <v>59602</v>
+        <v>30297</v>
       </c>
       <c r="P37" t="n">
-        <v>59602</v>
+        <v>31773</v>
       </c>
       <c r="Q37" t="n">
-        <v>76169</v>
+        <v>25037</v>
       </c>
       <c r="R37" t="n">
-        <v>76169</v>
+        <v>25801</v>
       </c>
       <c r="S37" t="n">
-        <v>76169</v>
+        <v>30035</v>
       </c>
       <c r="T37" t="n">
-        <v>76169</v>
+        <v>44428</v>
       </c>
       <c r="U37" t="n">
-        <v>76169</v>
+        <v>25679</v>
       </c>
       <c r="V37" t="n">
-        <v>76169</v>
+        <v>25801</v>
       </c>
       <c r="W37" t="n">
-        <v>76169</v>
+        <v>30332</v>
       </c>
       <c r="X37" t="n">
-        <v>76169</v>
+        <v>37428</v>
       </c>
       <c r="Y37" t="n">
-        <v>76169</v>
+        <v>160557</v>
       </c>
       <c r="Z37" t="n">
-        <v>76169</v>
+        <v>160709</v>
       </c>
       <c r="AA37" t="n">
-        <v>76169</v>
+        <v>161556</v>
       </c>
       <c r="AB37" t="n">
-        <v>76169</v>
+        <v>161717</v>
       </c>
       <c r="AC37" t="n">
-        <v>76169</v>
+        <v>163109</v>
       </c>
       <c r="AD37" t="n">
-        <v>76169</v>
+        <v>163724</v>
       </c>
       <c r="AE37" t="n">
-        <v>76169</v>
+        <v>164283</v>
       </c>
     </row>
     <row r="38">
@@ -7239,91 +7954,91 @@
         <v>1.83</v>
       </c>
       <c r="C38" t="n">
-        <v>1.83</v>
+        <v>2.27</v>
       </c>
       <c r="D38" t="n">
         <v>1.83</v>
       </c>
       <c r="E38" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="F38" t="n">
-        <v>1.83</v>
+        <v>3.53</v>
       </c>
       <c r="G38" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="H38" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="I38" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="J38" t="n">
         <v>1.83</v>
       </c>
       <c r="K38" t="n">
-        <v>1.83</v>
+        <v>3.86</v>
       </c>
       <c r="L38" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="M38" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="N38" t="n">
-        <v>1.83</v>
+        <v>4.45</v>
       </c>
       <c r="O38" t="n">
-        <v>1.83</v>
+        <v>4.68</v>
       </c>
       <c r="P38" t="n">
-        <v>1.83</v>
+        <v>4.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.94</v>
+        <v>1.97</v>
       </c>
       <c r="R38" t="n">
-        <v>3.94</v>
+        <v>1.97</v>
       </c>
       <c r="S38" t="n">
-        <v>3.94</v>
+        <v>1.97</v>
       </c>
       <c r="T38" t="n">
-        <v>3.94</v>
+        <v>1.97</v>
       </c>
       <c r="U38" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="V38" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="W38" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="X38" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="Y38" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
       <c r="AE38" t="n">
-        <v>3.94</v>
+        <v>20.01</v>
       </c>
     </row>
     <row r="39">
@@ -7333,94 +8048,94 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6.52</v>
+        <v>1.42</v>
       </c>
       <c r="C39" t="n">
-        <v>6.52</v>
+        <v>0.49</v>
       </c>
       <c r="D39" t="n">
-        <v>6.52</v>
+        <v>1.42</v>
       </c>
       <c r="E39" t="n">
-        <v>6.52</v>
+        <v>1.42</v>
       </c>
       <c r="F39" t="n">
-        <v>6.52</v>
+        <v>0.49</v>
       </c>
       <c r="G39" t="n">
-        <v>6.52</v>
+        <v>1.42</v>
       </c>
       <c r="H39" t="n">
-        <v>6.52</v>
+        <v>1.42</v>
       </c>
       <c r="I39" t="n">
-        <v>6.52</v>
+        <v>1.42</v>
       </c>
       <c r="J39" t="n">
-        <v>6.52</v>
+        <v>1.42</v>
       </c>
       <c r="K39" t="n">
-        <v>6.52</v>
+        <v>0.49</v>
       </c>
       <c r="L39" t="n">
-        <v>6.52</v>
+        <v>1.42</v>
       </c>
       <c r="M39" t="n">
-        <v>6.52</v>
+        <v>1.42</v>
       </c>
       <c r="N39" t="n">
-        <v>6.52</v>
+        <v>1.42</v>
       </c>
       <c r="O39" t="n">
-        <v>6.52</v>
+        <v>0.49</v>
       </c>
       <c r="P39" t="n">
-        <v>6.52</v>
+        <v>1.42</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.59</v>
+        <v>5.66</v>
       </c>
       <c r="R39" t="n">
-        <v>5.59</v>
+        <v>5.66</v>
       </c>
       <c r="S39" t="n">
-        <v>5.59</v>
+        <v>5.66</v>
       </c>
       <c r="T39" t="n">
-        <v>5.59</v>
+        <v>5.66</v>
       </c>
       <c r="U39" t="n">
-        <v>5.59</v>
+        <v>2.23</v>
       </c>
       <c r="V39" t="n">
-        <v>5.59</v>
+        <v>2.23</v>
       </c>
       <c r="W39" t="n">
-        <v>5.59</v>
+        <v>2.23</v>
       </c>
       <c r="X39" t="n">
-        <v>5.59</v>
+        <v>2.23</v>
       </c>
       <c r="Y39" t="n">
-        <v>5.59</v>
+        <v>9.17</v>
       </c>
       <c r="Z39" t="n">
-        <v>5.59</v>
+        <v>9.17</v>
       </c>
       <c r="AA39" t="n">
-        <v>5.59</v>
+        <v>9.17</v>
       </c>
       <c r="AB39" t="n">
-        <v>5.59</v>
+        <v>9.17</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.59</v>
+        <v>9.17</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.59</v>
+        <v>9.17</v>
       </c>
       <c r="AE39" t="n">
-        <v>5.59</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="40">
@@ -7430,94 +8145,94 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29.82</v>
+        <v>0.49</v>
       </c>
       <c r="C40" t="n">
-        <v>29.82</v>
+        <v>1.42</v>
       </c>
       <c r="D40" t="n">
-        <v>29.82</v>
+        <v>0.49</v>
       </c>
       <c r="E40" t="n">
-        <v>29.82</v>
+        <v>0.49</v>
       </c>
       <c r="F40" t="n">
-        <v>29.82</v>
+        <v>1.42</v>
       </c>
       <c r="G40" t="n">
-        <v>29.82</v>
+        <v>0.49</v>
       </c>
       <c r="H40" t="n">
-        <v>29.82</v>
+        <v>0.49</v>
       </c>
       <c r="I40" t="n">
-        <v>29.82</v>
+        <v>0.49</v>
       </c>
       <c r="J40" t="n">
-        <v>29.82</v>
+        <v>0.49</v>
       </c>
       <c r="K40" t="n">
-        <v>29.82</v>
+        <v>1.42</v>
       </c>
       <c r="L40" t="n">
-        <v>29.82</v>
+        <v>0.49</v>
       </c>
       <c r="M40" t="n">
-        <v>29.82</v>
+        <v>0.49</v>
       </c>
       <c r="N40" t="n">
-        <v>29.82</v>
+        <v>0.49</v>
       </c>
       <c r="O40" t="n">
-        <v>29.82</v>
+        <v>1.42</v>
       </c>
       <c r="P40" t="n">
-        <v>29.82</v>
+        <v>0.49</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.31</v>
+        <v>2.17</v>
       </c>
       <c r="R40" t="n">
-        <v>6.31</v>
+        <v>0.68</v>
       </c>
       <c r="S40" t="n">
-        <v>6.31</v>
+        <v>0.68</v>
       </c>
       <c r="T40" t="n">
-        <v>6.31</v>
+        <v>0.68</v>
       </c>
       <c r="U40" t="n">
-        <v>6.31</v>
+        <v>0.68</v>
       </c>
       <c r="V40" t="n">
-        <v>6.31</v>
+        <v>0.68</v>
       </c>
       <c r="W40" t="n">
-        <v>6.31</v>
+        <v>2.17</v>
       </c>
       <c r="X40" t="n">
-        <v>6.31</v>
+        <v>0.68</v>
       </c>
       <c r="Y40" t="n">
-        <v>6.31</v>
+        <v>5.6</v>
       </c>
       <c r="Z40" t="n">
-        <v>6.31</v>
+        <v>5.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>6.31</v>
+        <v>5.6</v>
       </c>
       <c r="AB40" t="n">
-        <v>6.31</v>
+        <v>5.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.31</v>
+        <v>5.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>6.31</v>
+        <v>5.6</v>
       </c>
       <c r="AE40" t="n">
-        <v>6.31</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="41">
@@ -7527,94 +8242,94 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>38.17</v>
+        <v>3.73</v>
       </c>
       <c r="C41" t="n">
-        <v>38.17</v>
+        <v>4.17</v>
       </c>
       <c r="D41" t="n">
-        <v>38.17</v>
+        <v>3.73</v>
       </c>
       <c r="E41" t="n">
-        <v>38.17</v>
+        <v>3.97</v>
       </c>
       <c r="F41" t="n">
-        <v>38.17</v>
+        <v>5.44</v>
       </c>
       <c r="G41" t="n">
-        <v>38.17</v>
+        <v>3.97</v>
       </c>
       <c r="H41" t="n">
-        <v>38.17</v>
+        <v>4.44</v>
       </c>
       <c r="I41" t="n">
-        <v>38.17</v>
+        <v>4.44</v>
       </c>
       <c r="J41" t="n">
-        <v>38.17</v>
+        <v>3.73</v>
       </c>
       <c r="K41" t="n">
-        <v>38.17</v>
+        <v>5.77</v>
       </c>
       <c r="L41" t="n">
-        <v>38.17</v>
+        <v>4.44</v>
       </c>
       <c r="M41" t="n">
-        <v>38.17</v>
+        <v>3.97</v>
       </c>
       <c r="N41" t="n">
-        <v>38.17</v>
+        <v>6.35</v>
       </c>
       <c r="O41" t="n">
-        <v>38.17</v>
+        <v>6.58</v>
       </c>
       <c r="P41" t="n">
-        <v>38.17</v>
+        <v>6.35</v>
       </c>
       <c r="Q41" t="n">
-        <v>15.84</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R41" t="n">
-        <v>15.84</v>
+        <v>8.31</v>
       </c>
       <c r="S41" t="n">
-        <v>15.84</v>
+        <v>8.31</v>
       </c>
       <c r="T41" t="n">
-        <v>15.84</v>
+        <v>8.31</v>
       </c>
       <c r="U41" t="n">
-        <v>15.84</v>
+        <v>6.82</v>
       </c>
       <c r="V41" t="n">
-        <v>15.84</v>
+        <v>6.82</v>
       </c>
       <c r="W41" t="n">
-        <v>15.84</v>
+        <v>8.31</v>
       </c>
       <c r="X41" t="n">
-        <v>15.84</v>
+        <v>6.82</v>
       </c>
       <c r="Y41" t="n">
-        <v>15.84</v>
+        <v>34.79</v>
       </c>
       <c r="Z41" t="n">
-        <v>15.84</v>
+        <v>34.79</v>
       </c>
       <c r="AA41" t="n">
-        <v>15.84</v>
+        <v>34.79</v>
       </c>
       <c r="AB41" t="n">
-        <v>15.84</v>
+        <v>34.79</v>
       </c>
       <c r="AC41" t="n">
-        <v>15.84</v>
+        <v>34.79</v>
       </c>
       <c r="AD41" t="n">
-        <v>15.84</v>
+        <v>34.79</v>
       </c>
       <c r="AE41" t="n">
-        <v>15.84</v>
+        <v>34.79</v>
       </c>
     </row>
     <row r="42">
@@ -7624,94 +8339,94 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>137602</v>
+        <v>69623</v>
       </c>
       <c r="C42" t="n">
-        <v>137602</v>
+        <v>70981</v>
       </c>
       <c r="D42" t="n">
-        <v>137602</v>
+        <v>72861</v>
       </c>
       <c r="E42" t="n">
-        <v>137602</v>
+        <v>72997</v>
       </c>
       <c r="F42" t="n">
-        <v>137602</v>
+        <v>74356</v>
       </c>
       <c r="G42" t="n">
-        <v>137602</v>
+        <v>75339</v>
       </c>
       <c r="H42" t="n">
-        <v>137602</v>
+        <v>76727</v>
       </c>
       <c r="I42" t="n">
-        <v>137602</v>
+        <v>76873</v>
       </c>
       <c r="J42" t="n">
-        <v>137602</v>
+        <v>77201</v>
       </c>
       <c r="K42" t="n">
-        <v>137602</v>
+        <v>78086</v>
       </c>
       <c r="L42" t="n">
-        <v>137602</v>
+        <v>78693</v>
       </c>
       <c r="M42" t="n">
-        <v>137602</v>
+        <v>79153</v>
       </c>
       <c r="N42" t="n">
-        <v>137602</v>
+        <v>80937</v>
       </c>
       <c r="O42" t="n">
-        <v>137602</v>
+        <v>82297</v>
       </c>
       <c r="P42" t="n">
-        <v>137602</v>
+        <v>83773</v>
       </c>
       <c r="Q42" t="n">
-        <v>220851</v>
+        <v>129719</v>
       </c>
       <c r="R42" t="n">
-        <v>220851</v>
+        <v>147801</v>
       </c>
       <c r="S42" t="n">
-        <v>220851</v>
+        <v>152035</v>
       </c>
       <c r="T42" t="n">
-        <v>220851</v>
+        <v>166428</v>
       </c>
       <c r="U42" t="n">
-        <v>220851</v>
+        <v>244179</v>
       </c>
       <c r="V42" t="n">
-        <v>220851</v>
+        <v>244301</v>
       </c>
       <c r="W42" t="n">
-        <v>220851</v>
+        <v>231514</v>
       </c>
       <c r="X42" t="n">
-        <v>220851</v>
+        <v>255928</v>
       </c>
       <c r="Y42" t="n">
-        <v>220851</v>
+        <v>274807</v>
       </c>
       <c r="Z42" t="n">
-        <v>220851</v>
+        <v>274959</v>
       </c>
       <c r="AA42" t="n">
-        <v>220851</v>
+        <v>275806</v>
       </c>
       <c r="AB42" t="n">
-        <v>220851</v>
+        <v>275967</v>
       </c>
       <c r="AC42" t="n">
-        <v>220851</v>
+        <v>277359</v>
       </c>
       <c r="AD42" t="n">
-        <v>220851</v>
+        <v>277974</v>
       </c>
       <c r="AE42" t="n">
-        <v>220851</v>
+        <v>278533</v>
       </c>
     </row>
     <row r="43">
@@ -7730,52 +8445,52 @@
         <v>219000</v>
       </c>
       <c r="E43" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="F43" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="G43" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="H43" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="I43" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="J43" t="n">
         <v>219000</v>
       </c>
       <c r="K43" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="L43" t="n">
-        <v>219000</v>
+        <v>215000</v>
       </c>
       <c r="M43" t="n">
-        <v>219000</v>
+        <v>218182</v>
       </c>
       <c r="N43" t="n">
-        <v>219000</v>
+        <v>220925</v>
       </c>
       <c r="O43" t="n">
-        <v>219000</v>
+        <v>220925</v>
       </c>
       <c r="P43" t="n">
-        <v>219000</v>
+        <v>220925</v>
       </c>
       <c r="Q43" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="R43" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="S43" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="T43" t="n">
-        <v>813000</v>
+        <v>1000000</v>
       </c>
       <c r="U43" t="n">
         <v>813000</v>
@@ -7790,25 +8505,25 @@
         <v>813000</v>
       </c>
       <c r="Y43" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="Z43" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="AA43" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="AB43" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="AC43" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="AD43" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
       <c r="AE43" t="n">
-        <v>813000</v>
+        <v>744073</v>
       </c>
     </row>
     <row r="44">
@@ -7818,94 +8533,94 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="C44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="D44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="E44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="F44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="G44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="H44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="I44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="J44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="K44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="L44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="M44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="N44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="O44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="P44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="Q44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="R44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="S44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="T44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="U44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="V44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="W44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="X44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="Y44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="Z44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="AA44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="AB44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="AC44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="AD44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
       <c r="AE44" t="n">
-        <v>129500</v>
+        <v>104500</v>
       </c>
     </row>
     <row r="45">
@@ -7915,94 +8630,94 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="C45" t="n">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="D45" t="n">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="E45" t="n">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="F45" t="n">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="G45" t="n">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="H45" t="n">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="I45" t="n">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="J45" t="n">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="K45" t="n">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="L45" t="n">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="M45" t="n">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="N45" t="n">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="O45" t="n">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="P45" t="n">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="Q45" t="n">
-        <v>329364</v>
+        <v>277864</v>
       </c>
       <c r="R45" t="n">
-        <v>329364</v>
+        <v>295182</v>
       </c>
       <c r="S45" t="n">
-        <v>329364</v>
+        <v>295182</v>
       </c>
       <c r="T45" t="n">
-        <v>329364</v>
+        <v>304000</v>
       </c>
       <c r="U45" t="n">
-        <v>329364</v>
+        <v>488182</v>
       </c>
       <c r="V45" t="n">
-        <v>329364</v>
+        <v>488182</v>
       </c>
       <c r="W45" t="n">
-        <v>329364</v>
+        <v>470864</v>
       </c>
       <c r="X45" t="n">
-        <v>329364</v>
+        <v>473182</v>
       </c>
       <c r="Y45" t="n">
-        <v>329364</v>
+        <v>282000</v>
       </c>
       <c r="Z45" t="n">
-        <v>329364</v>
+        <v>287000</v>
       </c>
       <c r="AA45" t="n">
-        <v>329364</v>
+        <v>297000</v>
       </c>
       <c r="AB45" t="n">
-        <v>329364</v>
+        <v>294214</v>
       </c>
       <c r="AC45" t="n">
-        <v>329364</v>
+        <v>293500</v>
       </c>
       <c r="AD45" t="n">
-        <v>329364</v>
+        <v>318500</v>
       </c>
       <c r="AE45" t="n">
-        <v>329364</v>
+        <v>279100</v>
       </c>
     </row>
     <row r="46">
@@ -8012,94 +8727,94 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>119204</v>
+        <v>35245</v>
       </c>
       <c r="C46" t="n">
-        <v>119204</v>
+        <v>37963</v>
       </c>
       <c r="D46" t="n">
-        <v>119204</v>
+        <v>41723</v>
       </c>
       <c r="E46" t="n">
-        <v>119204</v>
+        <v>41994</v>
       </c>
       <c r="F46" t="n">
-        <v>119204</v>
+        <v>44712</v>
       </c>
       <c r="G46" t="n">
-        <v>119204</v>
+        <v>46678</v>
       </c>
       <c r="H46" t="n">
-        <v>119204</v>
+        <v>49454</v>
       </c>
       <c r="I46" t="n">
-        <v>119204</v>
+        <v>49746</v>
       </c>
       <c r="J46" t="n">
-        <v>119204</v>
+        <v>50403</v>
       </c>
       <c r="K46" t="n">
-        <v>119204</v>
+        <v>52172</v>
       </c>
       <c r="L46" t="n">
-        <v>119204</v>
+        <v>53385</v>
       </c>
       <c r="M46" t="n">
-        <v>119204</v>
+        <v>54307</v>
       </c>
       <c r="N46" t="n">
-        <v>119204</v>
+        <v>57875</v>
       </c>
       <c r="O46" t="n">
-        <v>119204</v>
+        <v>60593</v>
       </c>
       <c r="P46" t="n">
-        <v>119204</v>
+        <v>63545</v>
       </c>
       <c r="Q46" t="n">
-        <v>152339</v>
+        <v>50073</v>
       </c>
       <c r="R46" t="n">
-        <v>152339</v>
+        <v>51603</v>
       </c>
       <c r="S46" t="n">
-        <v>152339</v>
+        <v>60071</v>
       </c>
       <c r="T46" t="n">
-        <v>152339</v>
+        <v>88856</v>
       </c>
       <c r="U46" t="n">
-        <v>152339</v>
+        <v>51358</v>
       </c>
       <c r="V46" t="n">
-        <v>152339</v>
+        <v>51603</v>
       </c>
       <c r="W46" t="n">
-        <v>152339</v>
+        <v>60664</v>
       </c>
       <c r="X46" t="n">
-        <v>152339</v>
+        <v>74856</v>
       </c>
       <c r="Y46" t="n">
-        <v>152339</v>
+        <v>321114</v>
       </c>
       <c r="Z46" t="n">
-        <v>152339</v>
+        <v>321419</v>
       </c>
       <c r="AA46" t="n">
-        <v>152339</v>
+        <v>323112</v>
       </c>
       <c r="AB46" t="n">
-        <v>152339</v>
+        <v>323433</v>
       </c>
       <c r="AC46" t="n">
-        <v>152339</v>
+        <v>326218</v>
       </c>
       <c r="AD46" t="n">
-        <v>152339</v>
+        <v>327448</v>
       </c>
       <c r="AE46" t="n">
-        <v>152339</v>
+        <v>328567</v>
       </c>
     </row>
     <row r="47">
@@ -8109,94 +8824,94 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>599704</v>
+        <v>489745</v>
       </c>
       <c r="C47" t="n">
-        <v>599704</v>
+        <v>492463</v>
       </c>
       <c r="D47" t="n">
-        <v>599704</v>
+        <v>496223</v>
       </c>
       <c r="E47" t="n">
-        <v>599704</v>
+        <v>495676</v>
       </c>
       <c r="F47" t="n">
-        <v>599704</v>
+        <v>498394</v>
       </c>
       <c r="G47" t="n">
-        <v>599704</v>
+        <v>500360</v>
       </c>
       <c r="H47" t="n">
-        <v>599704</v>
+        <v>499954</v>
       </c>
       <c r="I47" t="n">
-        <v>599704</v>
+        <v>500246</v>
       </c>
       <c r="J47" t="n">
-        <v>599704</v>
+        <v>504903</v>
       </c>
       <c r="K47" t="n">
-        <v>599704</v>
+        <v>502672</v>
       </c>
       <c r="L47" t="n">
-        <v>599704</v>
+        <v>503885</v>
       </c>
       <c r="M47" t="n">
-        <v>599704</v>
+        <v>507989</v>
       </c>
       <c r="N47" t="n">
-        <v>599704</v>
+        <v>514300</v>
       </c>
       <c r="O47" t="n">
-        <v>599704</v>
+        <v>517018</v>
       </c>
       <c r="P47" t="n">
-        <v>599704</v>
+        <v>519970</v>
       </c>
       <c r="Q47" t="n">
-        <v>1424203</v>
+        <v>1432437</v>
       </c>
       <c r="R47" t="n">
-        <v>1424203</v>
+        <v>1451285</v>
       </c>
       <c r="S47" t="n">
-        <v>1424203</v>
+        <v>1459753</v>
       </c>
       <c r="T47" t="n">
-        <v>1424203</v>
+        <v>1497356</v>
       </c>
       <c r="U47" t="n">
-        <v>1424203</v>
+        <v>1457040</v>
       </c>
       <c r="V47" t="n">
-        <v>1424203</v>
+        <v>1457285</v>
       </c>
       <c r="W47" t="n">
-        <v>1424203</v>
+        <v>1449028</v>
       </c>
       <c r="X47" t="n">
-        <v>1424203</v>
+        <v>1465538</v>
       </c>
       <c r="Y47" t="n">
-        <v>1424203</v>
+        <v>1451687</v>
       </c>
       <c r="Z47" t="n">
-        <v>1424203</v>
+        <v>1456992</v>
       </c>
       <c r="AA47" t="n">
-        <v>1424203</v>
+        <v>1468685</v>
       </c>
       <c r="AB47" t="n">
-        <v>1424203</v>
+        <v>1466220</v>
       </c>
       <c r="AC47" t="n">
-        <v>1424203</v>
+        <v>1468291</v>
       </c>
       <c r="AD47" t="n">
-        <v>1424203</v>
+        <v>1494521</v>
       </c>
       <c r="AE47" t="n">
-        <v>1424203</v>
+        <v>1456240</v>
       </c>
     </row>
     <row r="48">
@@ -8206,94 +8921,94 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>52.98</v>
+        <v>15.66</v>
       </c>
       <c r="C48" t="n">
-        <v>52.98</v>
+        <v>16.87</v>
       </c>
       <c r="D48" t="n">
-        <v>52.98</v>
+        <v>18.54</v>
       </c>
       <c r="E48" t="n">
-        <v>52.98</v>
+        <v>18.66</v>
       </c>
       <c r="F48" t="n">
-        <v>52.98</v>
+        <v>19.87</v>
       </c>
       <c r="G48" t="n">
-        <v>52.98</v>
+        <v>20.75</v>
       </c>
       <c r="H48" t="n">
-        <v>52.98</v>
+        <v>21.98</v>
       </c>
       <c r="I48" t="n">
-        <v>52.98</v>
+        <v>22.11</v>
       </c>
       <c r="J48" t="n">
-        <v>52.98</v>
+        <v>22.4</v>
       </c>
       <c r="K48" t="n">
-        <v>52.98</v>
+        <v>23.19</v>
       </c>
       <c r="L48" t="n">
-        <v>52.98</v>
+        <v>23.73</v>
       </c>
       <c r="M48" t="n">
-        <v>52.98</v>
+        <v>24.14</v>
       </c>
       <c r="N48" t="n">
-        <v>52.98</v>
+        <v>25.72</v>
       </c>
       <c r="O48" t="n">
-        <v>52.98</v>
+        <v>26.93</v>
       </c>
       <c r="P48" t="n">
-        <v>52.98</v>
+        <v>28.24</v>
       </c>
       <c r="Q48" t="n">
-        <v>67.70999999999999</v>
+        <v>22.25</v>
       </c>
       <c r="R48" t="n">
-        <v>67.70999999999999</v>
+        <v>22.93</v>
       </c>
       <c r="S48" t="n">
-        <v>67.70999999999999</v>
+        <v>26.7</v>
       </c>
       <c r="T48" t="n">
-        <v>67.70999999999999</v>
+        <v>39.49</v>
       </c>
       <c r="U48" t="n">
-        <v>67.70999999999999</v>
+        <v>22.83</v>
       </c>
       <c r="V48" t="n">
-        <v>67.70999999999999</v>
+        <v>22.93</v>
       </c>
       <c r="W48" t="n">
-        <v>67.70999999999999</v>
+        <v>26.96</v>
       </c>
       <c r="X48" t="n">
-        <v>67.70999999999999</v>
+        <v>33.27</v>
       </c>
       <c r="Y48" t="n">
-        <v>67.70999999999999</v>
+        <v>142.72</v>
       </c>
       <c r="Z48" t="n">
-        <v>67.70999999999999</v>
+        <v>142.85</v>
       </c>
       <c r="AA48" t="n">
-        <v>67.70999999999999</v>
+        <v>143.61</v>
       </c>
       <c r="AB48" t="n">
-        <v>67.70999999999999</v>
+        <v>143.75</v>
       </c>
       <c r="AC48" t="n">
-        <v>67.70999999999999</v>
+        <v>144.99</v>
       </c>
       <c r="AD48" t="n">
-        <v>67.70999999999999</v>
+        <v>145.53</v>
       </c>
       <c r="AE48" t="n">
-        <v>67.70999999999999</v>
+        <v>146.03</v>
       </c>
     </row>
     <row r="49">
@@ -8303,94 +9018,94 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>900296</v>
+        <v>1010255</v>
       </c>
       <c r="C49" t="n">
-        <v>900296</v>
+        <v>1007537</v>
       </c>
       <c r="D49" t="n">
-        <v>900296</v>
+        <v>1003777</v>
       </c>
       <c r="E49" t="n">
-        <v>900296</v>
+        <v>1004324</v>
       </c>
       <c r="F49" t="n">
-        <v>900296</v>
+        <v>1001606</v>
       </c>
       <c r="G49" t="n">
-        <v>900296</v>
+        <v>999640</v>
       </c>
       <c r="H49" t="n">
-        <v>900296</v>
+        <v>1000046</v>
       </c>
       <c r="I49" t="n">
-        <v>900296</v>
+        <v>999754</v>
       </c>
       <c r="J49" t="n">
-        <v>900296</v>
+        <v>995097</v>
       </c>
       <c r="K49" t="n">
-        <v>900296</v>
+        <v>997328</v>
       </c>
       <c r="L49" t="n">
-        <v>900296</v>
+        <v>996115</v>
       </c>
       <c r="M49" t="n">
-        <v>900296</v>
+        <v>992011</v>
       </c>
       <c r="N49" t="n">
-        <v>900296</v>
+        <v>985700</v>
       </c>
       <c r="O49" t="n">
-        <v>900296</v>
+        <v>982982</v>
       </c>
       <c r="P49" t="n">
-        <v>900296</v>
+        <v>980030</v>
       </c>
       <c r="Q49" t="n">
-        <v>75797</v>
+        <v>67563</v>
       </c>
       <c r="R49" t="n">
-        <v>75797</v>
+        <v>48715</v>
       </c>
       <c r="S49" t="n">
-        <v>75797</v>
+        <v>40247</v>
       </c>
       <c r="T49" t="n">
-        <v>75797</v>
+        <v>2644</v>
       </c>
       <c r="U49" t="n">
-        <v>75797</v>
+        <v>42960</v>
       </c>
       <c r="V49" t="n">
-        <v>75797</v>
+        <v>42715</v>
       </c>
       <c r="W49" t="n">
-        <v>75797</v>
+        <v>50972</v>
       </c>
       <c r="X49" t="n">
-        <v>75797</v>
+        <v>34462</v>
       </c>
       <c r="Y49" t="n">
-        <v>75797</v>
+        <v>48313</v>
       </c>
       <c r="Z49" t="n">
-        <v>75797</v>
+        <v>43008</v>
       </c>
       <c r="AA49" t="n">
-        <v>75797</v>
+        <v>31315</v>
       </c>
       <c r="AB49" t="n">
-        <v>75797</v>
+        <v>33780</v>
       </c>
       <c r="AC49" t="n">
-        <v>75797</v>
+        <v>31709</v>
       </c>
       <c r="AD49" t="n">
-        <v>75797</v>
+        <v>5479</v>
       </c>
       <c r="AE49" t="n">
-        <v>75797</v>
+        <v>43760</v>
       </c>
     </row>
     <row r="50">
